--- a/Side Bar Files/GWD Data/WTP.xlsx
+++ b/Side Bar Files/GWD Data/WTP.xlsx
@@ -719,13 +719,21 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -768,7 +776,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -890,6 +900,7 @@
       <sheetName val="3 Core Cable PRICE"/>
       <sheetName val="ARS Filter Media"/>
       <sheetName val="BW Casing Pipes"/>
+      <sheetName val="Electrical Essentials"/>
       <sheetName val="GI on Wall PRICE"/>
       <sheetName val="GI wo Trench"/>
       <sheetName val="GI With Trench PRICE"/>
@@ -897,16 +908,19 @@
       <sheetName val="Gravel for TWC"/>
       <sheetName val="Gutter&amp;Clamp"/>
       <sheetName val="HDPE Pipe PRICE"/>
+      <sheetName val="HP Erection and Pullout"/>
       <sheetName val="HP Repair Labour"/>
       <sheetName val="HP Repair Spares"/>
       <sheetName val="Hydrants"/>
       <sheetName val="Iron Structure"/>
+      <sheetName val="Lock"/>
       <sheetName val="Metallic PH"/>
       <sheetName val="Motor Starter GWD"/>
       <sheetName val="Motor Starter Monoblock"/>
       <sheetName val="Motor Starter PRICE"/>
       <sheetName val="Other Fittings PRICE"/>
       <sheetName val="Panel Board"/>
+      <sheetName val="Pump Cover"/>
       <sheetName val="Pump Erection "/>
       <sheetName val="Pump Pullout"/>
       <sheetName val="PVC Fittings"/>
@@ -967,6 +981,10 @@
       <sheetData sheetId="37"/>
       <sheetData sheetId="38"/>
       <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1268,7 +1286,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2910B234-8157-4F93-B70A-8057F2B0B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00ACC9CF-E16D-4A5E-8729-EBBDF5E0B9A7}">
   <dimension ref="A1:G465"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
@@ -7587,7 +7605,7 @@
         <v>103</v>
       </c>
       <c r="E411" s="24">
-        <f>'[1]PVC wo Trench'!F145</f>
+        <f>'[1]PVC wo Trench'!F167</f>
         <v>120.22</v>
       </c>
       <c r="F411" s="12" t="s">
@@ -7610,7 +7628,7 @@
         <v>103</v>
       </c>
       <c r="E412" s="24">
-        <f>'[1]PVC wo Trench'!F154</f>
+        <f>'[1]PVC wo Trench'!F176</f>
         <v>29.66</v>
       </c>
       <c r="F412" s="12" t="s">
@@ -7646,7 +7664,7 @@
         <v>103</v>
       </c>
       <c r="E414" s="24">
-        <f>'[1]PVC wo Trench'!F101</f>
+        <f>'[1]PVC wo Trench'!F123</f>
         <v>112.20</v>
       </c>
       <c r="F414" s="12" t="s">
@@ -7669,7 +7687,7 @@
         <v>103</v>
       </c>
       <c r="E415" s="24">
-        <f>'[1]PVC wo Trench'!F110</f>
+        <f>'[1]PVC wo Trench'!F132</f>
         <v>29.66</v>
       </c>
       <c r="F415" s="12" t="s">
@@ -7705,7 +7723,7 @@
         <v>103</v>
       </c>
       <c r="E417" s="24">
-        <f>'[1]PVC wo Trench'!F35</f>
+        <f>'[1]PVC wo Trench'!F57</f>
         <v>86.82</v>
       </c>
       <c r="F417" s="12" t="s">
@@ -7728,7 +7746,7 @@
         <v>103</v>
       </c>
       <c r="E418" s="24">
-        <f>'[1]PVC wo Trench'!F44</f>
+        <f>'[1]PVC wo Trench'!F66</f>
         <v>29.66</v>
       </c>
       <c r="F418" s="12" t="s">
@@ -7764,7 +7782,7 @@
         <v>103</v>
       </c>
       <c r="E420" s="24">
-        <f>'[1]PVC wo Trench'!F13</f>
+        <f>'[1]PVC wo Trench'!F35</f>
         <v>64.11</v>
       </c>
       <c r="F420" s="12" t="s">
@@ -7787,7 +7805,7 @@
         <v>103</v>
       </c>
       <c r="E421" s="24">
-        <f>'[1]PVC wo Trench'!F22</f>
+        <f>'[1]PVC wo Trench'!F44</f>
         <v>29.66</v>
       </c>
       <c r="F421" s="12" t="s">

--- a/Side Bar Files/GWD Data/WTP.xlsx
+++ b/Side Bar Files/GWD Data/WTP.xlsx
@@ -12,27 +12,33 @@
   <externalReferences>
     <externalReference r:id="rId5"/>
   </externalReferences>
-  <definedNames/>
+  <definedNames>
+    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+  </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="142">
   <si>
     <t>GROUND WATER DEPARTMENT REVISED RATES FOR WATER TREATMENT PLANTS</t>
   </si>
   <si>
-    <t>I.  FRP VESSEL - (Fibre Reinforced Polymer Vessel)</t>
+    <t>I. FRP VESSEL - (Fibre Reinforced Polymer Vessel)</t>
   </si>
   <si>
     <t>(i)</t>
   </si>
   <si>
-    <t xml:space="preserve">Supplying, assembling, fibre reinforced polymer vessel (FRP) size  (14" Dia 65" Height) Weight - 21 kg, Tank Volume - 150 liter, Material- Polyethylene, Max Pressure -150 PSI, Max Vacuum- 5" Hg, Max temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom  including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge </t>
-  </si>
-  <si>
-    <t>FRP-1465 vessel (MR)</t>
+    <t>Supplying, assembling, fibre reinforced polymer vessel (FRP) size (14" Dia 65" Height) Weight - 21 kg, Tank Volume - 150 liter, Material- Polyethylene, Max Pressure -150 PSI, Max Vacuum- 5" Hg, Max temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>FRP-1465 vessel</t>
   </si>
   <si>
     <t>no</t>
@@ -50,7 +56,7 @@
     <t>CPOH 15%</t>
   </si>
   <si>
-    <t xml:space="preserve">Total    </t>
+    <t xml:space="preserve">Total </t>
   </si>
   <si>
     <t>0116</t>
@@ -77,64 +83,64 @@
     <t>(ii)</t>
   </si>
   <si>
-    <t xml:space="preserve">Supplying, assembling, fibre reinforced polymer vessel (FRP) size  (16" Dia 65" Height) Weight - 22 kg, Tank Volume - 185 liter, Material- Polyethylene, Max Pressure -150 PSI, Max Vacuum- 5" Hg, Max temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom  including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge </t>
-  </si>
-  <si>
-    <t>FRP-1665 vessel (MR)</t>
+    <t>Supplying, assembling, fibre reinforced polymer vessel (FRP) size (16" Dia 65" Height) Weight - 22 kg, Tank Volume - 185 liter, Material- Polyethylene, Max Pressure -150 PSI, Max Vacuum- 5" Hg, Max temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>FRP-1665 vessel</t>
   </si>
   <si>
     <t>(iii)</t>
   </si>
   <si>
-    <t xml:space="preserve">Supplying, assembling, fibre reinforced polymer vessel (FRP) Size-(18" Dia 65" Height), Weight-30kg,  Tank Volume - 242 liter , Material- Polyethylene,  Max Pressure -150 PSI, Max Vacuum- 5" Hg, Max Temperature -49'c, Capacity- 1000-10000 L, opening at top &amp; bottom  including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge </t>
-  </si>
-  <si>
-    <t>FRP-1865 vessel   (MR)</t>
+    <t>Supplying, assembling, fibre reinforced polymer vessel (FRP) Size-(18" Dia 65" Height), Weight-30kg, Tank Volume - 242 liter , Material- Polyethylene, Max Pressure -150 PSI, Max Vacuum- 5" Hg, Max Temperature -49'c, Capacity- 1000-10000 L, opening at top &amp; bottom including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>FRP-1865 vessel</t>
   </si>
   <si>
     <t>(iv)</t>
   </si>
   <si>
-    <t xml:space="preserve">Supplying, assembling, fibre reinforced polymer vessel (FRP) Size-(21" Dia 62" Height), Weight-43kg,  Tank Volume -318 liter , Material- Polyethylene,  Max Pressure -150 PSI, Max Vacuum- 5" Hg, Temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge </t>
-  </si>
-  <si>
-    <t>FRP-2162 vessel (MR)</t>
+    <t>Supplying, assembling, fibre reinforced polymer vessel (FRP) Size-(21" Dia 62" Height), Weight-43kg, Tank Volume -318 liter , Material- Polyethylene, Max Pressure -150 PSI, Max Vacuum- 5" Hg, Temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>FRP-2162 vessel</t>
   </si>
   <si>
     <t>(v)</t>
   </si>
   <si>
-    <t xml:space="preserve">Supplying, assembling, fibre reinforced polymer vessel (FRP) Size-(24" Dia 72" Height), Weight-49kg,  Tank Volume -451 liter , Material- Polyethylene,  Max Pressure -150 PSI, Max Vacuum- 5" Hg, Temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge </t>
-  </si>
-  <si>
-    <t>FRP-2472 vessel  (MR)</t>
+    <t>Supplying, assembling, fibre reinforced polymer vessel (FRP) Size-(24" Dia 72" Height), Weight-49kg, Tank Volume -451 liter , Material- Polyethylene, Max Pressure -150 PSI, Max Vacuum- 5" Hg, Temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>FRP-2472 vessel</t>
   </si>
   <si>
     <t>(vi)</t>
   </si>
   <si>
-    <t xml:space="preserve">Supplying, assembling, fibre reinforced polymer vessel (FRP) Size-(30" Dia 72" Height), Weight-90kg,  Tank Volume -708 liter , Material- Polyethylene,  Max Pressure -150 PSI, Max Vacuum- 5" Hg, Temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge </t>
-  </si>
-  <si>
-    <t>FRP-3072 vessel  (MR)</t>
+    <t>Supplying, assembling, fibre reinforced polymer vessel (FRP) Size-(30" Dia 72" Height), Weight-90kg, Tank Volume -708 liter , Material- Polyethylene, Max Pressure -150 PSI, Max Vacuum- 5" Hg, Temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>FRP-3072 vessel</t>
   </si>
   <si>
     <t>(vii)</t>
   </si>
   <si>
-    <t xml:space="preserve">Supplying, assembling, fibre reinforced polymer vessel (FRP) Size-(36" Dia 72" Height), Weight-105kg,  Tank Volume -1020 liter , Material- Polyethylene,  Max Pressure -150 PSI, Max Vacuum- 5" Hg, Temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge </t>
-  </si>
-  <si>
-    <t>FRP-3672 vessel  (MR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II.  MPV- (Multi port valve)    </t>
-  </si>
-  <si>
-    <t>Supplying, assembling, manually operated multi port valve 40 NB Material -PVC, Max pressure - 4kg/cm2,   including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
-  </si>
-  <si>
-    <t>MPV-40 NB  (MR)</t>
+    <t>Supplying, assembling, fibre reinforced polymer vessel (FRP) Size-(36" Dia 72" Height), Weight-105kg, Tank Volume -1020 liter , Material- Polyethylene, Max Pressure -150 PSI, Max Vacuum- 5" Hg, Temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>FRP-3672 vessel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II. MPV- (Multi port valve) </t>
+  </si>
+  <si>
+    <t>Supplying, assembling, manually operated multi port valve 40 NB Material -PVC, Max pressure - 4kg/cm2, including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>MPV-40 NB</t>
   </si>
   <si>
     <t>9988</t>
@@ -146,130 +152,130 @@
     <t>LS</t>
   </si>
   <si>
-    <t>Supplying, assembling, manually operated multi port valve flower type 50NB Material -PVC, Max pressure - 4kg/cm2,   including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
-  </si>
-  <si>
-    <t>MPV-50 NB  (MR)</t>
-  </si>
-  <si>
-    <t>Supplying, assembling, multi port valve 65 NB Manually Material -PVC, Max pressure - 4kg/cm2,   including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
-  </si>
-  <si>
-    <t>MPV-65 NB (MR)</t>
-  </si>
-  <si>
-    <t>III.  Distributer</t>
+    <t>Supplying, assembling, manually operated multi port valve flower type 50NB Material -PVC, Max pressure - 4kg/cm2, including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>MPV-50 NB</t>
+  </si>
+  <si>
+    <t>Supplying, assembling, multi port valve 65 NB Manually Material -PVC, Max pressure - 4kg/cm2, including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>MPV-65 NB</t>
+  </si>
+  <si>
+    <t>III. Distributer</t>
   </si>
   <si>
     <t>Supplying, assembling, distributer 40 NB including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
-    <t>Distributer-40 NB  (MR)</t>
+    <t>Distributer-40 NB</t>
   </si>
   <si>
     <t>Supplying, assembling, distributer 50 NB including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
-    <t>Distributer-50 NB  (MR)</t>
+    <t>Distributer-50 NB</t>
   </si>
   <si>
     <t>Supplying, assembling, distributer 65 NB including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
-    <t>Distributer-65 NB (MR)</t>
-  </si>
-  <si>
-    <t>IV.  Dosing pump</t>
+    <t>Distributer-65 NB</t>
+  </si>
+  <si>
+    <t>IV. Dosing pump</t>
   </si>
   <si>
     <t>Supplying, assembling, and fixing Electrically operated Diaphragm type dosing pump 10 lph including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
-    <t>Dosing pump-10 lph  (MR)</t>
+    <t>Dosing pump-10 lph</t>
   </si>
   <si>
     <t>Supplying, assembling, and fixing Electrically operated Diaphragm type dosing pump 40 lph including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
-    <t>Dosing pump-40 lph  (MR)</t>
-  </si>
-  <si>
-    <t>V.  Feed pump</t>
-  </si>
-  <si>
-    <t>Supplying, assembling, and fixing single Phase Pure Copper , Self priming  monoblock feed  pump 1Hp including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
-  </si>
-  <si>
-    <t>1 HP monoblock feed pump (ISI)  (MR)</t>
-  </si>
-  <si>
-    <t>Supplying, assembling, and fixing single Phase Pure Copper , Self priming  monoblock feed  pump 1.5Hp including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
-  </si>
-  <si>
-    <t>1.5 HP monoblock feed pump (ISI)  (MR)</t>
-  </si>
-  <si>
-    <t>Supplying, assembling, and fixing single Phase Pure Copper , Self priming monoblock feed  pump 2Hp including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
-  </si>
-  <si>
-    <t>2 HP monoblock feed pump (ISI)  (MR)</t>
-  </si>
-  <si>
-    <t>VI.  Sludge pump</t>
-  </si>
-  <si>
-    <t>Supplying, assembling, and fixing sludge pump 1Hp, 220v, Max head 20m , 750W, Max flw 15000 lph  including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
-  </si>
-  <si>
-    <t>1 HP sludge pump(ISI)  (MR)</t>
-  </si>
-  <si>
-    <t>VII.  UV Plant</t>
-  </si>
-  <si>
-    <t>Supplying, assembling, and fixing 5000 lph Stainless Steel  UV Plant including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
-  </si>
-  <si>
-    <t>UV plant- 5000 lph  (MR)</t>
+    <t>Dosing pump-40 lph</t>
+  </si>
+  <si>
+    <t>V. Feed pump</t>
+  </si>
+  <si>
+    <t>Supplying, assembling, and fixing single Phase Pure Copper , Self priming monoblock feed pump 1Hp including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>1 HP monoblock feed pump (ISI)</t>
+  </si>
+  <si>
+    <t>Supplying, assembling, and fixing single Phase Pure Copper , Self priming monoblock feed pump 1.5Hp including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>1.5 HP monoblock feed pump (ISI)</t>
+  </si>
+  <si>
+    <t>Supplying, assembling, and fixing single Phase Pure Copper , Self priming monoblock feed pump 2Hp including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>2 HP monoblock feed pump (ISI)</t>
+  </si>
+  <si>
+    <t>VI. Sludge pump</t>
+  </si>
+  <si>
+    <t>Supplying, assembling, and fixing sludge pump 1Hp, 220v, Max head 20m , 750W, Max flw 15000 lph including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>1 HP sludge pump(ISI)</t>
+  </si>
+  <si>
+    <t>VII. UV Plant</t>
+  </si>
+  <si>
+    <t>Supplying, assembling, and fixing 5000 lph Stainless Steel UV Plant including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>UV plant- 5000 lph</t>
   </si>
   <si>
     <t>Supplying, assembling, and fixing 10000 lph UV Plant including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
-    <t>UV plant- 10000 lph  (MR)</t>
+    <t>UV plant- 10000 lph</t>
   </si>
   <si>
     <t>Supplying, assembling, and fixing 15000 lph UV Plant including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
-    <t>UV plant- 15000 lph  (MR)</t>
-  </si>
-  <si>
-    <t>VIII.  Automatic plant controller</t>
-  </si>
-  <si>
-    <t>Supplying, assembling, and fixing automatic treatment plant controller including automation of plant,  hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
-  </si>
-  <si>
-    <t>Full automatic controller kit   (MR)</t>
-  </si>
-  <si>
-    <t>IX.  Pressure Gauge</t>
+    <t>UV plant- 15000 lph</t>
+  </si>
+  <si>
+    <t>VIII. Automatic plant controller</t>
+  </si>
+  <si>
+    <t>Supplying, assembling, and fixing automatic treatment plant controller including automation of plant, hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
+  </si>
+  <si>
+    <t>Full automatic controller kit</t>
+  </si>
+  <si>
+    <t>IX. Pressure Gauge</t>
   </si>
   <si>
     <t>Supplying, assembling, and fixing 63mm pressure gauge including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
-    <t>Pressure gauge- 63mm   (MR)</t>
-  </si>
-  <si>
-    <t>X.  Filter Medium   (MR)</t>
+    <t>Pressure gauge- 63mm</t>
+  </si>
+  <si>
+    <t>X. Filter Medium (MR)</t>
   </si>
   <si>
     <t>Supplying and filling, Silex, Fine sand and Pressure sand including hire &amp; labour charges, carriage etc complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
-    <t>Silex, Fine sand and Pressure sand- Rate for   (MR)</t>
+    <t>Silex, Fine sand and Pressure sand</t>
   </si>
   <si>
     <t>Kg</t>
@@ -278,22 +284,22 @@
     <t>Supplying and filling, Katalox iron remover including hire &amp; labour charges, carriage etc. all complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
-    <t>Katalox iron remover (MR)</t>
+    <t>Katalox iron remover</t>
   </si>
   <si>
     <t>Supplying and filling, Activated carbon IV 1050 including hire &amp; labour charges, carriage etc. all complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
-    <t>Activated carbon IV 1050  (MR)</t>
-  </si>
-  <si>
-    <t>XI.  Dosing Chemicals</t>
+    <t>Activated carbon IV 1050</t>
+  </si>
+  <si>
+    <t>XI. Dosing Chemicals</t>
   </si>
   <si>
     <t>Supplying and filling, liquid chlorine including hire &amp; labour charges, carriage etc. all complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
-    <t>Liquid chlorine  (MR)</t>
+    <t>Liquid chlorine</t>
   </si>
   <si>
     <t>kg</t>
@@ -305,10 +311,10 @@
     <t>Supplying and filling, liquid alum including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
-    <t>Liquid alum   (MR)</t>
-  </si>
-  <si>
-    <t>XII.  Plant Installation</t>
+    <t>Liquid alum</t>
+  </si>
+  <si>
+    <t>XII. Plant Installation</t>
   </si>
   <si>
     <t>Plant installation charges including labour and materials for supports, stand, PVC connection pipes, PVC valves, air valves etc complete. all complete</t>
@@ -320,7 +326,7 @@
     <t>Materials 1</t>
   </si>
   <si>
-    <t>0</t>
+    <t>GWDDR042</t>
   </si>
   <si>
     <t>Providing and fixing PVC pipes includes jointing of pipes with one step PVC solvent cement &amp; testing of joints complete as per direction of Engineer in Charge. 
@@ -339,14 +345,23 @@
     <t>Labour</t>
   </si>
   <si>
+    <t>GWDDR040</t>
+  </si>
+  <si>
     <t>Providing and fixing PVC pipes includes jointing of pipes with one step PVC solvent cement &amp; testing of joints complete as per direction of Engineer in Charge. 
 40 mm dia 10 KGF/cm2</t>
   </si>
   <si>
+    <t>GWDDR037</t>
+  </si>
+  <si>
     <t>Providing and fixing PVC pipes includes jointing of pipes with one step PVC solvent cement &amp; testing of joints complete as per direction of Engineer in Charge. 
 32 mm dia 10 KGF/cm2</t>
   </si>
   <si>
+    <t>GWDDR036</t>
+  </si>
+  <si>
     <t>Providing and fixing PVC pipes includes jointing of pipes with one step PVC solvent cement &amp; testing of joints complete as per direction of Engineer in Charge. 
 25 mm dia 10 KGF/cm2</t>
   </si>
@@ -396,16 +411,16 @@
     <t>Air Valve, GM, Indian Standard, Class 2, 20mm ( ¾" )</t>
   </si>
   <si>
-    <t>Screw, nail, Nut &amp; Bolt etc (MR)</t>
-  </si>
-  <si>
-    <t>Wire 4 mm (MR)</t>
-  </si>
-  <si>
-    <t>20 W LED tube light (MR)</t>
-  </si>
-  <si>
-    <t>252x 5 MS angle for support and stand (20m) (MR)</t>
+    <t>Screw, nail, Nut &amp; Bolt etc</t>
+  </si>
+  <si>
+    <t>Wire 4 mm</t>
+  </si>
+  <si>
+    <t>20 W LED tube light</t>
+  </si>
+  <si>
+    <t>252x 5 MS angle for support and stand (20m)</t>
   </si>
   <si>
     <t>3</t>
@@ -426,7 +441,7 @@
     <t xml:space="preserve"> 0114</t>
   </si>
   <si>
-    <t>XIII.  Plant Maintenance/ AMC</t>
+    <t>XIII. Plant Maintenance/ AMC</t>
   </si>
   <si>
     <t>Plant inspection, maintenance, cleaning, back wash, sludge removal, sample collection and correction of Dosing etc complete, and water quality checking (except filling chemicals)</t>
@@ -689,25 +704,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -741,7 +742,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -806,11 +807,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -907,7 +908,6 @@
       <sheetName val="GI Works"/>
       <sheetName val="Gravel for TWC"/>
       <sheetName val="Gutter&amp;Clamp"/>
-      <sheetName val="HDPE Pipe PRICE"/>
       <sheetName val="HP Erection and Pullout"/>
       <sheetName val="HP Repair Labour"/>
       <sheetName val="HP Repair Spares"/>
@@ -927,9 +927,11 @@
       <sheetName val="PVC Fittings PRICE"/>
       <sheetName val="PVC on Wall (Concealed) PRICE"/>
       <sheetName val="PVC on Wall PRICE"/>
+      <sheetName val="PVC on Wall"/>
+      <sheetName val="PVC wo Trench PRICE"/>
       <sheetName val="PVC wo Trench"/>
+      <sheetName val="PVC With Trench PRICE"/>
       <sheetName val="PVC With Trench"/>
-      <sheetName val="PVC With Trench PRICE"/>
       <sheetName val="Scaffolding"/>
       <sheetName val="Services"/>
       <sheetName val="TW Casing Pipes"/>
@@ -938,6 +940,9 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
+      <sheetName val="Derived"/>
+      <sheetName val="LMR"/>
+      <sheetName val="PAMR39"/>
       <sheetName val="ZCost Index"/>
     </sheetNames>
     <sheetDataSet>
@@ -985,6 +990,10 @@
       <sheetData sheetId="41"/>
       <sheetData sheetId="42"/>
       <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1286,7 +1295,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00ACC9CF-E16D-4A5E-8729-EBBDF5E0B9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98489C21-0790-4944-9758-54ABDDCDBAA6}">
   <dimension ref="A1:G465"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
@@ -1326,21 +1335,23 @@
       <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7" ht="12.75">
-      <c r="A4" s="9"/>
+      <c r="A4" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="B4" s="10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="11">
         <v>1</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="11">
         <v>16500</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" s="13">
         <f>E4*C4</f>
@@ -1350,7 +1361,7 @@
     <row r="5" spans="1:7" ht="12.75">
       <c r="A5" s="9"/>
       <c r="B5" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
@@ -1364,7 +1375,7 @@
     <row r="6" spans="1:7" ht="12.75">
       <c r="A6" s="9"/>
       <c r="B6" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -1378,7 +1389,7 @@
     <row r="7" spans="1:7" ht="12.75">
       <c r="A7" s="9"/>
       <c r="B7" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
@@ -1392,7 +1403,7 @@
     <row r="8" spans="1:7" ht="12.75">
       <c r="A8" s="9"/>
       <c r="B8" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="17"/>
@@ -1405,22 +1416,22 @@
     </row>
     <row r="9" spans="1:7" ht="12.75">
       <c r="A9" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="11">
         <v>0.30</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" s="11">
         <v>784</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" s="13">
         <f>C9*E9</f>
@@ -1429,22 +1440,22 @@
     </row>
     <row r="10" spans="1:7" ht="12.75">
       <c r="A10" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="11">
         <v>0.30</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" s="11">
         <v>645</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10" s="13">
         <f>C10*E10</f>
@@ -1454,7 +1465,7 @@
     <row r="11" spans="1:7" ht="12.75">
       <c r="A11" s="9"/>
       <c r="B11" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -1468,7 +1479,7 @@
     <row r="12" spans="1:7" ht="12.75">
       <c r="A12" s="9"/>
       <c r="B12" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -1482,7 +1493,7 @@
     <row r="13" spans="1:7" ht="12.75">
       <c r="A13" s="9"/>
       <c r="B13" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -1496,7 +1507,7 @@
     <row r="14" spans="1:7" ht="12.75">
       <c r="A14" s="9"/>
       <c r="B14" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -1510,7 +1521,7 @@
     <row r="15" spans="1:7" ht="12.75">
       <c r="A15" s="9"/>
       <c r="B15" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="17"/>
@@ -1535,10 +1546,10 @@
     </row>
     <row r="17" spans="1:7" ht="12.75">
       <c r="A17" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -1547,21 +1558,23 @@
       <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7" ht="12.75">
-      <c r="A18" s="7"/>
+      <c r="A18" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B18" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="11">
         <v>1</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="11">
         <v>26500</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" s="13">
         <f>E18*C18</f>
@@ -1571,7 +1584,7 @@
     <row r="19" spans="1:7" ht="12.75">
       <c r="A19" s="9"/>
       <c r="B19" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -1585,7 +1598,7 @@
     <row r="20" spans="1:7" ht="12.75">
       <c r="A20" s="9"/>
       <c r="B20" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
@@ -1599,7 +1612,7 @@
     <row r="21" spans="1:7" ht="12.75">
       <c r="A21" s="9"/>
       <c r="B21" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
@@ -1613,7 +1626,7 @@
     <row r="22" spans="1:7" ht="12.75">
       <c r="A22" s="9"/>
       <c r="B22" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" s="16"/>
       <c r="D22" s="17"/>
@@ -1626,22 +1639,22 @@
     </row>
     <row r="23" spans="1:7" ht="12.75">
       <c r="A23" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C23" s="11">
         <v>0.30</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" s="11">
         <v>784</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G23" s="13">
         <f>C23*E23</f>
@@ -1650,22 +1663,22 @@
     </row>
     <row r="24" spans="1:7" ht="12.75">
       <c r="A24" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C24" s="11">
         <v>0.30</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24" s="11">
         <v>645</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G24" s="13">
         <f>C24*E24</f>
@@ -1675,7 +1688,7 @@
     <row r="25" spans="1:7" ht="12.75">
       <c r="A25" s="9"/>
       <c r="B25" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
@@ -1689,7 +1702,7 @@
     <row r="26" spans="1:7" ht="12.75">
       <c r="A26" s="9"/>
       <c r="B26" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
@@ -1703,7 +1716,7 @@
     <row r="27" spans="1:7" ht="12.75">
       <c r="A27" s="9"/>
       <c r="B27" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
@@ -1717,7 +1730,7 @@
     <row r="28" spans="1:7" ht="12.75">
       <c r="A28" s="9"/>
       <c r="B28" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -1731,7 +1744,7 @@
     <row r="29" spans="1:7" ht="12.75">
       <c r="A29" s="9"/>
       <c r="B29" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="17"/>
@@ -1756,10 +1769,10 @@
     </row>
     <row r="31" spans="1:7" ht="12.75">
       <c r="A31" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -1768,21 +1781,23 @@
       <c r="G31" s="6"/>
     </row>
     <row r="32" spans="1:7" ht="12.75">
-      <c r="A32" s="7"/>
+      <c r="A32" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B32" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C32" s="11">
         <v>1</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32" s="11">
         <v>36000</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G32" s="13">
         <f>E32*C32</f>
@@ -1792,7 +1807,7 @@
     <row r="33" spans="1:7" ht="12.75">
       <c r="A33" s="9"/>
       <c r="B33" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
@@ -1806,7 +1821,7 @@
     <row r="34" spans="1:7" ht="12.75">
       <c r="A34" s="9"/>
       <c r="B34" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
@@ -1820,7 +1835,7 @@
     <row r="35" spans="1:7" ht="12.75">
       <c r="A35" s="9"/>
       <c r="B35" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
@@ -1834,7 +1849,7 @@
     <row r="36" spans="1:7" ht="12.75">
       <c r="A36" s="9"/>
       <c r="B36" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="16"/>
       <c r="D36" s="17"/>
@@ -1847,22 +1862,22 @@
     </row>
     <row r="37" spans="1:7" ht="12.75">
       <c r="A37" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C37" s="11">
         <v>0.30</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E37" s="11">
         <v>784</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G37" s="13">
         <f>C37*E37</f>
@@ -1871,22 +1886,22 @@
     </row>
     <row r="38" spans="1:7" ht="12.75">
       <c r="A38" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C38" s="11">
         <v>0.30</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E38" s="11">
         <v>645</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G38" s="13">
         <f>C38*E38</f>
@@ -1896,7 +1911,7 @@
     <row r="39" spans="1:7" ht="12.75">
       <c r="A39" s="9"/>
       <c r="B39" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
@@ -1910,7 +1925,7 @@
     <row r="40" spans="1:7" ht="12.75">
       <c r="A40" s="9"/>
       <c r="B40" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
@@ -1924,7 +1939,7 @@
     <row r="41" spans="1:7" ht="12.75">
       <c r="A41" s="9"/>
       <c r="B41" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
@@ -1938,7 +1953,7 @@
     <row r="42" spans="1:7" ht="12.75">
       <c r="A42" s="9"/>
       <c r="B42" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
@@ -1952,7 +1967,7 @@
     <row r="43" spans="1:7" ht="12.75">
       <c r="A43" s="9"/>
       <c r="B43" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="17"/>
@@ -1977,10 +1992,10 @@
     </row>
     <row r="45" spans="1:7" ht="12.75">
       <c r="A45" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -1989,21 +2004,23 @@
       <c r="G45" s="6"/>
     </row>
     <row r="46" spans="1:7" ht="12.75">
-      <c r="A46" s="7"/>
+      <c r="A46" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B46" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" s="11">
         <v>1</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E46" s="11">
         <v>40500</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G46" s="13">
         <f>E46*C46</f>
@@ -2013,7 +2030,7 @@
     <row r="47" spans="1:7" ht="12.75">
       <c r="A47" s="9"/>
       <c r="B47" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
@@ -2027,7 +2044,7 @@
     <row r="48" spans="1:7" ht="12.75">
       <c r="A48" s="9"/>
       <c r="B48" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
@@ -2041,7 +2058,7 @@
     <row r="49" spans="1:7" ht="12.75">
       <c r="A49" s="9"/>
       <c r="B49" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
@@ -2055,7 +2072,7 @@
     <row r="50" spans="1:7" ht="12.75">
       <c r="A50" s="9"/>
       <c r="B50" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C50" s="16"/>
       <c r="D50" s="17"/>
@@ -2068,22 +2085,22 @@
     </row>
     <row r="51" spans="1:7" ht="12.75">
       <c r="A51" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C51" s="11">
         <v>0.30</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E51" s="11">
         <v>784</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G51" s="13">
         <f>C51*E51</f>
@@ -2092,22 +2109,22 @@
     </row>
     <row r="52" spans="1:7" ht="12.75">
       <c r="A52" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C52" s="11">
         <v>0.30</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E52" s="11">
         <v>645</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G52" s="13">
         <f>C52*E52</f>
@@ -2117,7 +2134,7 @@
     <row r="53" spans="1:7" ht="12.75">
       <c r="A53" s="9"/>
       <c r="B53" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
@@ -2131,7 +2148,7 @@
     <row r="54" spans="1:7" ht="12.75">
       <c r="A54" s="9"/>
       <c r="B54" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
@@ -2145,7 +2162,7 @@
     <row r="55" spans="1:7" ht="12.75">
       <c r="A55" s="9"/>
       <c r="B55" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
@@ -2159,7 +2176,7 @@
     <row r="56" spans="1:7" ht="12.75">
       <c r="A56" s="9"/>
       <c r="B56" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
@@ -2173,7 +2190,7 @@
     <row r="57" spans="1:7" ht="12.75">
       <c r="A57" s="9"/>
       <c r="B57" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C57" s="16"/>
       <c r="D57" s="17"/>
@@ -2198,10 +2215,10 @@
     </row>
     <row r="59" spans="1:7" ht="12.75">
       <c r="A59" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
@@ -2210,21 +2227,23 @@
       <c r="G59" s="6"/>
     </row>
     <row r="60" spans="1:7" ht="12.75">
-      <c r="A60" s="7"/>
+      <c r="A60" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B60" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C60" s="11">
         <v>1</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E60" s="11">
         <v>49000</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G60" s="13">
         <f>E60*C60</f>
@@ -2234,7 +2253,7 @@
     <row r="61" spans="1:7" ht="12.75">
       <c r="A61" s="9"/>
       <c r="B61" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
@@ -2248,7 +2267,7 @@
     <row r="62" spans="1:7" ht="12.75">
       <c r="A62" s="9"/>
       <c r="B62" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
@@ -2262,7 +2281,7 @@
     <row r="63" spans="1:7" ht="12.75">
       <c r="A63" s="9"/>
       <c r="B63" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
@@ -2276,7 +2295,7 @@
     <row r="64" spans="1:7" ht="12.75">
       <c r="A64" s="9"/>
       <c r="B64" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C64" s="16"/>
       <c r="D64" s="17"/>
@@ -2289,22 +2308,22 @@
     </row>
     <row r="65" spans="1:7" ht="12.75">
       <c r="A65" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C65" s="11">
         <v>0.30</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E65" s="11">
         <v>784</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G65" s="13">
         <f>C65*E65</f>
@@ -2313,22 +2332,22 @@
     </row>
     <row r="66" spans="1:7" ht="12.75">
       <c r="A66" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C66" s="11">
         <v>0.40</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E66" s="11">
         <v>645</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G66" s="13">
         <f>C66*E66</f>
@@ -2338,7 +2357,7 @@
     <row r="67" spans="1:7" ht="12.75">
       <c r="A67" s="9"/>
       <c r="B67" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
@@ -2352,7 +2371,7 @@
     <row r="68" spans="1:7" ht="12.75">
       <c r="A68" s="9"/>
       <c r="B68" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
@@ -2366,7 +2385,7 @@
     <row r="69" spans="1:7" ht="12.75">
       <c r="A69" s="9"/>
       <c r="B69" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
@@ -2380,7 +2399,7 @@
     <row r="70" spans="1:7" ht="12.75">
       <c r="A70" s="9"/>
       <c r="B70" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
@@ -2394,7 +2413,7 @@
     <row r="71" spans="1:7" ht="12.75">
       <c r="A71" s="9"/>
       <c r="B71" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C71" s="16"/>
       <c r="D71" s="17"/>
@@ -2419,10 +2438,10 @@
     </row>
     <row r="73" spans="1:7" ht="12.75">
       <c r="A73" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
@@ -2431,21 +2450,23 @@
       <c r="G73" s="6"/>
     </row>
     <row r="74" spans="1:7" ht="12.75">
-      <c r="A74" s="7"/>
+      <c r="A74" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B74" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C74" s="11">
         <v>1</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E74" s="11">
         <v>62000</v>
       </c>
       <c r="F74" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G74" s="13">
         <f>E74*C74</f>
@@ -2455,7 +2476,7 @@
     <row r="75" spans="1:7" ht="12.75">
       <c r="A75" s="9"/>
       <c r="B75" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C75" s="11"/>
       <c r="D75" s="11"/>
@@ -2469,7 +2490,7 @@
     <row r="76" spans="1:7" ht="12.75">
       <c r="A76" s="9"/>
       <c r="B76" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
@@ -2483,7 +2504,7 @@
     <row r="77" spans="1:7" ht="12.75">
       <c r="A77" s="9"/>
       <c r="B77" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
@@ -2497,7 +2518,7 @@
     <row r="78" spans="1:7" ht="12.75">
       <c r="A78" s="9"/>
       <c r="B78" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C78" s="16"/>
       <c r="D78" s="17"/>
@@ -2510,22 +2531,22 @@
     </row>
     <row r="79" spans="1:7" ht="12.75">
       <c r="A79" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C79" s="11">
         <v>0.50</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E79" s="11">
         <v>784</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G79" s="13">
         <f>C79*E79</f>
@@ -2534,22 +2555,22 @@
     </row>
     <row r="80" spans="1:7" ht="12.75">
       <c r="A80" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C80" s="11">
         <v>0.40</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E80" s="11">
         <v>645</v>
       </c>
       <c r="F80" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G80" s="13">
         <f>C80*E80</f>
@@ -2559,7 +2580,7 @@
     <row r="81" spans="1:7" ht="12.75">
       <c r="A81" s="9"/>
       <c r="B81" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
@@ -2573,7 +2594,7 @@
     <row r="82" spans="1:7" ht="12.75">
       <c r="A82" s="9"/>
       <c r="B82" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
@@ -2587,7 +2608,7 @@
     <row r="83" spans="1:7" ht="12.75">
       <c r="A83" s="9"/>
       <c r="B83" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
@@ -2601,7 +2622,7 @@
     <row r="84" spans="1:7" ht="12.75">
       <c r="A84" s="9"/>
       <c r="B84" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
@@ -2615,7 +2636,7 @@
     <row r="85" spans="1:7" ht="12.75">
       <c r="A85" s="9"/>
       <c r="B85" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C85" s="16"/>
       <c r="D85" s="17"/>
@@ -2640,10 +2661,10 @@
     </row>
     <row r="87" spans="1:7" ht="12.75">
       <c r="A87" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
@@ -2652,21 +2673,23 @@
       <c r="G87" s="6"/>
     </row>
     <row r="88" spans="1:7" ht="12.75">
-      <c r="A88" s="7"/>
+      <c r="A88" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B88" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C88" s="11">
         <v>1</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E88" s="11">
         <v>83000</v>
       </c>
       <c r="F88" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G88" s="13">
         <f>E88*C88</f>
@@ -2676,7 +2699,7 @@
     <row r="89" spans="1:7" ht="12.75">
       <c r="A89" s="9"/>
       <c r="B89" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
@@ -2690,7 +2713,7 @@
     <row r="90" spans="1:7" ht="12.75">
       <c r="A90" s="9"/>
       <c r="B90" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
@@ -2704,7 +2727,7 @@
     <row r="91" spans="1:7" ht="12.75">
       <c r="A91" s="9"/>
       <c r="B91" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
@@ -2718,7 +2741,7 @@
     <row r="92" spans="1:7" ht="12.75">
       <c r="A92" s="9"/>
       <c r="B92" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C92" s="16"/>
       <c r="D92" s="17"/>
@@ -2731,22 +2754,22 @@
     </row>
     <row r="93" spans="1:7" ht="12.75">
       <c r="A93" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C93" s="11">
         <v>0.50</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E93" s="11">
         <v>784</v>
       </c>
       <c r="F93" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G93" s="13">
         <f>C93*E93</f>
@@ -2755,22 +2778,22 @@
     </row>
     <row r="94" spans="1:7" ht="12.75">
       <c r="A94" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C94" s="11">
         <v>0.40</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E94" s="11">
         <v>645</v>
       </c>
       <c r="F94" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G94" s="13">
         <f>C94*E94</f>
@@ -2780,7 +2803,7 @@
     <row r="95" spans="1:7" ht="12.75">
       <c r="A95" s="9"/>
       <c r="B95" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
@@ -2794,7 +2817,7 @@
     <row r="96" spans="1:7" ht="12.75">
       <c r="A96" s="9"/>
       <c r="B96" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
@@ -2808,7 +2831,7 @@
     <row r="97" spans="1:7" ht="12.75">
       <c r="A97" s="9"/>
       <c r="B97" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
@@ -2822,7 +2845,7 @@
     <row r="98" spans="1:7" ht="12.75">
       <c r="A98" s="9"/>
       <c r="B98" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
@@ -2836,7 +2859,7 @@
     <row r="99" spans="1:7" ht="12.75">
       <c r="A99" s="9"/>
       <c r="B99" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C99" s="16"/>
       <c r="D99" s="17"/>
@@ -2861,7 +2884,7 @@
     </row>
     <row r="101" spans="1:7" ht="12.75">
       <c r="A101" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -2875,7 +2898,7 @@
         <v>2</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
@@ -2884,21 +2907,23 @@
       <c r="G102" s="6"/>
     </row>
     <row r="103" spans="1:7" ht="12.75">
-      <c r="A103" s="7"/>
+      <c r="A103" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B103" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C103" s="11">
         <v>1</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E103" s="11">
         <v>7677</v>
       </c>
       <c r="F103" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G103" s="13">
         <f>E103*C103</f>
@@ -2908,7 +2933,7 @@
     <row r="104" spans="1:7" ht="12.75">
       <c r="A104" s="7"/>
       <c r="B104" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
@@ -2922,7 +2947,7 @@
     <row r="105" spans="1:7" ht="12.75">
       <c r="A105" s="7"/>
       <c r="B105" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C105" s="11"/>
       <c r="D105" s="11"/>
@@ -2936,7 +2961,7 @@
     <row r="106" spans="1:7" ht="12.75">
       <c r="A106" s="7"/>
       <c r="B106" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="11"/>
@@ -2950,7 +2975,7 @@
     <row r="107" spans="1:7" ht="12.75">
       <c r="A107" s="7"/>
       <c r="B107" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C107" s="16"/>
       <c r="D107" s="17"/>
@@ -2963,22 +2988,22 @@
     </row>
     <row r="108" spans="1:7" ht="12.75">
       <c r="A108" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C108" s="11">
         <v>15.50</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E108" s="11">
         <v>2.12</v>
       </c>
       <c r="F108" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G108" s="13">
         <f>C108*E108</f>
@@ -2988,7 +3013,7 @@
     <row r="109" spans="1:7" ht="12.75">
       <c r="A109" s="7"/>
       <c r="B109" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C109" s="11"/>
       <c r="D109" s="11"/>
@@ -3002,7 +3027,7 @@
     <row r="110" spans="1:7" ht="12.75">
       <c r="A110" s="7"/>
       <c r="B110" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11"/>
@@ -3016,7 +3041,7 @@
     <row r="111" spans="1:7" ht="12.75">
       <c r="A111" s="7"/>
       <c r="B111" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="11"/>
@@ -3030,7 +3055,7 @@
     <row r="112" spans="1:7" ht="12.75">
       <c r="A112" s="7"/>
       <c r="B112" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C112" s="11"/>
       <c r="D112" s="11"/>
@@ -3044,7 +3069,7 @@
     <row r="113" spans="1:7" ht="12.75">
       <c r="A113" s="7"/>
       <c r="B113" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C113" s="16"/>
       <c r="D113" s="17"/>
@@ -3069,10 +3094,10 @@
     </row>
     <row r="115" spans="1:7" ht="12.75">
       <c r="A115" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C115" s="5"/>
       <c r="D115" s="5"/>
@@ -3081,21 +3106,23 @@
       <c r="G115" s="6"/>
     </row>
     <row r="116" spans="1:7" ht="12.75">
-      <c r="A116" s="7"/>
+      <c r="A116" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B116" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C116" s="11">
         <v>1</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E116" s="11">
         <v>9620</v>
       </c>
       <c r="F116" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G116" s="13">
         <f>E116*C116</f>
@@ -3105,7 +3132,7 @@
     <row r="117" spans="1:7" ht="12.75">
       <c r="A117" s="7"/>
       <c r="B117" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C117" s="11"/>
       <c r="D117" s="11"/>
@@ -3119,7 +3146,7 @@
     <row r="118" spans="1:7" ht="12.75">
       <c r="A118" s="7"/>
       <c r="B118" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="11"/>
@@ -3133,7 +3160,7 @@
     <row r="119" spans="1:7" ht="12.75">
       <c r="A119" s="7"/>
       <c r="B119" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C119" s="11"/>
       <c r="D119" s="11"/>
@@ -3147,7 +3174,7 @@
     <row r="120" spans="1:7" ht="12.75">
       <c r="A120" s="7"/>
       <c r="B120" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C120" s="16"/>
       <c r="D120" s="17"/>
@@ -3160,22 +3187,22 @@
     </row>
     <row r="121" spans="1:7" ht="12.75">
       <c r="A121" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C121" s="11">
         <v>15.50</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E121" s="11">
         <v>2.12</v>
       </c>
       <c r="F121" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G121" s="13">
         <f>C121*E121</f>
@@ -3185,7 +3212,7 @@
     <row r="122" spans="1:7" ht="12.75">
       <c r="A122" s="7"/>
       <c r="B122" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C122" s="11"/>
       <c r="D122" s="11"/>
@@ -3199,7 +3226,7 @@
     <row r="123" spans="1:7" ht="12.75">
       <c r="A123" s="7"/>
       <c r="B123" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C123" s="11"/>
       <c r="D123" s="11"/>
@@ -3213,7 +3240,7 @@
     <row r="124" spans="1:7" ht="12.75">
       <c r="A124" s="7"/>
       <c r="B124" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C124" s="11"/>
       <c r="D124" s="11"/>
@@ -3227,7 +3254,7 @@
     <row r="125" spans="1:7" ht="12.75">
       <c r="A125" s="7"/>
       <c r="B125" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C125" s="11"/>
       <c r="D125" s="11"/>
@@ -3241,7 +3268,7 @@
     <row r="126" spans="1:7" ht="12.75">
       <c r="A126" s="7"/>
       <c r="B126" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C126" s="16"/>
       <c r="D126" s="17"/>
@@ -3266,10 +3293,10 @@
     </row>
     <row r="128" spans="1:7" ht="12.75">
       <c r="A128" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C128" s="5"/>
       <c r="D128" s="5"/>
@@ -3278,21 +3305,23 @@
       <c r="G128" s="6"/>
     </row>
     <row r="129" spans="1:7" ht="12.75">
-      <c r="A129" s="7"/>
+      <c r="A129" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B129" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C129" s="11">
         <v>1</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E129" s="11">
         <v>11487</v>
       </c>
       <c r="F129" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G129" s="13">
         <f>E129*C129</f>
@@ -3302,7 +3331,7 @@
     <row r="130" spans="1:7" ht="12.75">
       <c r="A130" s="7"/>
       <c r="B130" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C130" s="11"/>
       <c r="D130" s="11"/>
@@ -3316,7 +3345,7 @@
     <row r="131" spans="1:7" ht="12.75">
       <c r="A131" s="7"/>
       <c r="B131" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C131" s="11"/>
       <c r="D131" s="11"/>
@@ -3330,7 +3359,7 @@
     <row r="132" spans="1:7" ht="12.75">
       <c r="A132" s="7"/>
       <c r="B132" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C132" s="11"/>
       <c r="D132" s="11"/>
@@ -3344,7 +3373,7 @@
     <row r="133" spans="1:7" ht="12.75">
       <c r="A133" s="7"/>
       <c r="B133" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C133" s="16"/>
       <c r="D133" s="17"/>
@@ -3357,22 +3386,22 @@
     </row>
     <row r="134" spans="1:7" ht="12.75">
       <c r="A134" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C134" s="11">
         <v>15.50</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E134" s="11">
         <v>2.12</v>
       </c>
       <c r="F134" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G134" s="13">
         <f>C134*E134</f>
@@ -3382,7 +3411,7 @@
     <row r="135" spans="1:7" ht="12.75">
       <c r="A135" s="7"/>
       <c r="B135" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C135" s="11"/>
       <c r="D135" s="11"/>
@@ -3396,7 +3425,7 @@
     <row r="136" spans="1:7" ht="12.75">
       <c r="A136" s="7"/>
       <c r="B136" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C136" s="11"/>
       <c r="D136" s="11"/>
@@ -3410,7 +3439,7 @@
     <row r="137" spans="1:7" ht="12.75">
       <c r="A137" s="7"/>
       <c r="B137" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C137" s="11"/>
       <c r="D137" s="11"/>
@@ -3424,7 +3453,7 @@
     <row r="138" spans="1:7" ht="12.75">
       <c r="A138" s="7"/>
       <c r="B138" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C138" s="11"/>
       <c r="D138" s="11"/>
@@ -3438,7 +3467,7 @@
     <row r="139" spans="1:7" ht="12.75">
       <c r="A139" s="7"/>
       <c r="B139" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C139" s="16"/>
       <c r="D139" s="17"/>
@@ -3463,7 +3492,7 @@
     </row>
     <row r="141" spans="1:7" ht="12.75">
       <c r="A141" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
@@ -3477,7 +3506,7 @@
         <v>2</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C142" s="5"/>
       <c r="D142" s="5"/>
@@ -3486,21 +3515,23 @@
       <c r="G142" s="6"/>
     </row>
     <row r="143" spans="1:7" ht="12.75">
-      <c r="A143" s="7"/>
+      <c r="A143" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B143" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C143" s="11">
         <v>1</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E143" s="11">
         <v>4530</v>
       </c>
       <c r="F143" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G143" s="13">
         <f>C143*E143</f>
@@ -3510,7 +3541,7 @@
     <row r="144" spans="1:7" ht="12.75">
       <c r="A144" s="7"/>
       <c r="B144" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C144" s="11"/>
       <c r="D144" s="11"/>
@@ -3524,7 +3555,7 @@
     <row r="145" spans="1:7" ht="12.75">
       <c r="A145" s="7"/>
       <c r="B145" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C145" s="11"/>
       <c r="D145" s="11"/>
@@ -3538,7 +3569,7 @@
     <row r="146" spans="1:7" ht="12.75">
       <c r="A146" s="7"/>
       <c r="B146" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C146" s="11"/>
       <c r="D146" s="11"/>
@@ -3552,7 +3583,7 @@
     <row r="147" spans="1:7" ht="12.75">
       <c r="A147" s="7"/>
       <c r="B147" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C147" s="16"/>
       <c r="D147" s="17"/>
@@ -3565,22 +3596,22 @@
     </row>
     <row r="148" spans="1:7" ht="12.75">
       <c r="A148" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C148" s="11">
         <v>15.50</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E148" s="11">
         <v>2.12</v>
       </c>
       <c r="F148" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G148" s="13">
         <f>C148*E148</f>
@@ -3590,7 +3621,7 @@
     <row r="149" spans="1:7" ht="12.75">
       <c r="A149" s="7"/>
       <c r="B149" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C149" s="11"/>
       <c r="D149" s="11"/>
@@ -3604,7 +3635,7 @@
     <row r="150" spans="1:7" ht="12.75">
       <c r="A150" s="7"/>
       <c r="B150" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C150" s="11"/>
       <c r="D150" s="11"/>
@@ -3618,7 +3649,7 @@
     <row r="151" spans="1:7" ht="12.75">
       <c r="A151" s="7"/>
       <c r="B151" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C151" s="11"/>
       <c r="D151" s="11"/>
@@ -3632,7 +3663,7 @@
     <row r="152" spans="1:7" ht="12.75">
       <c r="A152" s="7"/>
       <c r="B152" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C152" s="11"/>
       <c r="D152" s="11"/>
@@ -3646,7 +3677,7 @@
     <row r="153" spans="1:7" ht="12.75">
       <c r="A153" s="7"/>
       <c r="B153" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C153" s="16"/>
       <c r="D153" s="17"/>
@@ -3671,10 +3702,10 @@
     </row>
     <row r="155" spans="1:7" ht="12.75">
       <c r="A155" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C155" s="5"/>
       <c r="D155" s="5"/>
@@ -3683,21 +3714,23 @@
       <c r="G155" s="6"/>
     </row>
     <row r="156" spans="1:7" ht="12.75">
-      <c r="A156" s="7"/>
+      <c r="A156" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B156" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C156" s="11">
         <v>1</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E156" s="11">
         <v>6750</v>
       </c>
       <c r="F156" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G156" s="13">
         <f>C156*E156</f>
@@ -3707,7 +3740,7 @@
     <row r="157" spans="1:7" ht="12.75">
       <c r="A157" s="7"/>
       <c r="B157" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C157" s="11"/>
       <c r="D157" s="11"/>
@@ -3721,7 +3754,7 @@
     <row r="158" spans="1:7" ht="12.75">
       <c r="A158" s="7"/>
       <c r="B158" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C158" s="11"/>
       <c r="D158" s="11"/>
@@ -3735,7 +3768,7 @@
     <row r="159" spans="1:7" ht="12.75">
       <c r="A159" s="7"/>
       <c r="B159" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C159" s="11"/>
       <c r="D159" s="11"/>
@@ -3749,7 +3782,7 @@
     <row r="160" spans="1:7" ht="12.75">
       <c r="A160" s="7"/>
       <c r="B160" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C160" s="16"/>
       <c r="D160" s="17"/>
@@ -3762,22 +3795,22 @@
     </row>
     <row r="161" spans="1:7" ht="12.75">
       <c r="A161" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B161" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C161" s="11">
         <v>15.50</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E161" s="11">
         <v>2.12</v>
       </c>
       <c r="F161" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G161" s="13">
         <f>C161*E161</f>
@@ -3787,7 +3820,7 @@
     <row r="162" spans="1:7" ht="12.75">
       <c r="A162" s="7"/>
       <c r="B162" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C162" s="11"/>
       <c r="D162" s="11"/>
@@ -3801,7 +3834,7 @@
     <row r="163" spans="1:7" ht="12.75">
       <c r="A163" s="7"/>
       <c r="B163" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C163" s="11"/>
       <c r="D163" s="11"/>
@@ -3815,7 +3848,7 @@
     <row r="164" spans="1:7" ht="12.75">
       <c r="A164" s="7"/>
       <c r="B164" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C164" s="11"/>
       <c r="D164" s="11"/>
@@ -3829,7 +3862,7 @@
     <row r="165" spans="1:7" ht="12.75">
       <c r="A165" s="7"/>
       <c r="B165" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C165" s="11"/>
       <c r="D165" s="11"/>
@@ -3843,7 +3876,7 @@
     <row r="166" spans="1:7" ht="12.75">
       <c r="A166" s="7"/>
       <c r="B166" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C166" s="16"/>
       <c r="D166" s="17"/>
@@ -3868,10 +3901,10 @@
     </row>
     <row r="168" spans="1:7" ht="12.75">
       <c r="A168" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C168" s="5"/>
       <c r="D168" s="5"/>
@@ -3880,21 +3913,23 @@
       <c r="G168" s="6"/>
     </row>
     <row r="169" spans="1:7" ht="12.75">
-      <c r="A169" s="7"/>
+      <c r="A169" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B169" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C169" s="11">
         <v>1</v>
       </c>
       <c r="D169" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E169" s="11">
         <v>10266</v>
       </c>
       <c r="F169" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G169" s="13">
         <f>C169*E169</f>
@@ -3904,7 +3939,7 @@
     <row r="170" spans="1:7" ht="12.75">
       <c r="A170" s="7"/>
       <c r="B170" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C170" s="11"/>
       <c r="D170" s="11"/>
@@ -3918,7 +3953,7 @@
     <row r="171" spans="1:7" ht="12.75">
       <c r="A171" s="7"/>
       <c r="B171" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C171" s="11"/>
       <c r="D171" s="11"/>
@@ -3932,7 +3967,7 @@
     <row r="172" spans="1:7" ht="12.75">
       <c r="A172" s="7"/>
       <c r="B172" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C172" s="11"/>
       <c r="D172" s="11"/>
@@ -3946,7 +3981,7 @@
     <row r="173" spans="1:7" ht="12.75">
       <c r="A173" s="7"/>
       <c r="B173" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C173" s="16"/>
       <c r="D173" s="17"/>
@@ -3959,22 +3994,22 @@
     </row>
     <row r="174" spans="1:7" ht="12.75">
       <c r="A174" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C174" s="11">
         <v>15.50</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E174" s="11">
         <v>2.12</v>
       </c>
       <c r="F174" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G174" s="13">
         <f>C174*E174</f>
@@ -3984,7 +4019,7 @@
     <row r="175" spans="1:7" ht="12.75">
       <c r="A175" s="7"/>
       <c r="B175" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C175" s="11"/>
       <c r="D175" s="11"/>
@@ -3998,7 +4033,7 @@
     <row r="176" spans="1:7" ht="12.75">
       <c r="A176" s="7"/>
       <c r="B176" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C176" s="11"/>
       <c r="D176" s="11"/>
@@ -4012,7 +4047,7 @@
     <row r="177" spans="1:7" ht="12.75">
       <c r="A177" s="7"/>
       <c r="B177" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C177" s="11"/>
       <c r="D177" s="11"/>
@@ -4026,7 +4061,7 @@
     <row r="178" spans="1:7" ht="12.75">
       <c r="A178" s="7"/>
       <c r="B178" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C178" s="11"/>
       <c r="D178" s="11"/>
@@ -4040,7 +4075,7 @@
     <row r="179" spans="1:7" ht="12.75">
       <c r="A179" s="7"/>
       <c r="B179" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C179" s="16"/>
       <c r="D179" s="17"/>
@@ -4065,7 +4100,7 @@
     </row>
     <row r="181" spans="1:7" ht="12.75">
       <c r="A181" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
@@ -4079,7 +4114,7 @@
         <v>2</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C182" s="5"/>
       <c r="D182" s="5"/>
@@ -4088,21 +4123,23 @@
       <c r="G182" s="6"/>
     </row>
     <row r="183" spans="1:7" ht="12.75">
-      <c r="A183" s="7"/>
+      <c r="A183" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B183" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C183" s="11">
         <v>1</v>
       </c>
       <c r="D183" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E183" s="11">
         <v>15662</v>
       </c>
       <c r="F183" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G183" s="13">
         <f>C183*E183</f>
@@ -4112,7 +4149,7 @@
     <row r="184" spans="1:7" ht="12.75">
       <c r="A184" s="9"/>
       <c r="B184" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C184" s="11"/>
       <c r="D184" s="11"/>
@@ -4126,7 +4163,7 @@
     <row r="185" spans="1:7" ht="12.75">
       <c r="A185" s="9"/>
       <c r="B185" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C185" s="11"/>
       <c r="D185" s="11"/>
@@ -4140,7 +4177,7 @@
     <row r="186" spans="1:7" ht="12.75">
       <c r="A186" s="9"/>
       <c r="B186" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C186" s="11"/>
       <c r="D186" s="11"/>
@@ -4154,7 +4191,7 @@
     <row r="187" spans="1:7" ht="12.75">
       <c r="A187" s="9"/>
       <c r="B187" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C187" s="11"/>
       <c r="D187" s="11"/>
@@ -4167,22 +4204,22 @@
     </row>
     <row r="188" spans="1:7" ht="12.75">
       <c r="A188" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C188" s="11">
         <v>0.20</v>
       </c>
       <c r="D188" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E188" s="11">
         <v>784</v>
       </c>
       <c r="F188" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G188" s="13">
         <f>C188*E188</f>
@@ -4191,22 +4228,22 @@
     </row>
     <row r="189" spans="1:7" ht="12.75">
       <c r="A189" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C189" s="11">
         <v>0.20</v>
       </c>
       <c r="D189" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E189" s="11">
         <v>645</v>
       </c>
       <c r="F189" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G189" s="13">
         <f>C189*E189</f>
@@ -4216,7 +4253,7 @@
     <row r="190" spans="1:7" ht="12.75">
       <c r="A190" s="9"/>
       <c r="B190" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C190" s="11"/>
       <c r="D190" s="11"/>
@@ -4230,7 +4267,7 @@
     <row r="191" spans="1:7" ht="12.75">
       <c r="A191" s="9"/>
       <c r="B191" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C191" s="11"/>
       <c r="D191" s="11"/>
@@ -4244,7 +4281,7 @@
     <row r="192" spans="1:7" ht="12.75">
       <c r="A192" s="9"/>
       <c r="B192" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C192" s="11"/>
       <c r="D192" s="11"/>
@@ -4258,7 +4295,7 @@
     <row r="193" spans="1:7" ht="12.75">
       <c r="A193" s="9"/>
       <c r="B193" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C193" s="11"/>
       <c r="D193" s="11"/>
@@ -4272,7 +4309,7 @@
     <row r="194" spans="1:7" ht="12.75">
       <c r="A194" s="9"/>
       <c r="B194" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C194" s="16"/>
       <c r="D194" s="11"/>
@@ -4297,10 +4334,10 @@
     </row>
     <row r="196" spans="1:7" ht="12.75">
       <c r="A196" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C196" s="5"/>
       <c r="D196" s="5"/>
@@ -4309,21 +4346,23 @@
       <c r="G196" s="6"/>
     </row>
     <row r="197" spans="1:7" ht="12.75">
-      <c r="A197" s="7"/>
+      <c r="A197" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B197" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C197" s="11">
         <v>1</v>
       </c>
       <c r="D197" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E197" s="11">
         <v>42500</v>
       </c>
       <c r="F197" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G197" s="13">
         <f>C197*E197</f>
@@ -4333,7 +4372,7 @@
     <row r="198" spans="1:7" ht="12.75">
       <c r="A198" s="9"/>
       <c r="B198" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C198" s="11"/>
       <c r="D198" s="11"/>
@@ -4347,7 +4386,7 @@
     <row r="199" spans="1:7" ht="12.75">
       <c r="A199" s="9"/>
       <c r="B199" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C199" s="11"/>
       <c r="D199" s="11"/>
@@ -4361,7 +4400,7 @@
     <row r="200" spans="1:7" ht="12.75">
       <c r="A200" s="9"/>
       <c r="B200" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C200" s="11"/>
       <c r="D200" s="11"/>
@@ -4375,7 +4414,7 @@
     <row r="201" spans="1:7" ht="12.75">
       <c r="A201" s="9"/>
       <c r="B201" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C201" s="11"/>
       <c r="D201" s="11"/>
@@ -4388,22 +4427,22 @@
     </row>
     <row r="202" spans="1:7" ht="12.75">
       <c r="A202" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C202" s="11">
         <v>0.20</v>
       </c>
       <c r="D202" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E202" s="11">
         <v>784</v>
       </c>
       <c r="F202" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G202" s="13">
         <f>C202*E202</f>
@@ -4412,22 +4451,22 @@
     </row>
     <row r="203" spans="1:7" ht="12.75">
       <c r="A203" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C203" s="11">
         <v>0.20</v>
       </c>
       <c r="D203" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E203" s="11">
         <v>645</v>
       </c>
       <c r="F203" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G203" s="13">
         <f>C203*E203</f>
@@ -4437,7 +4476,7 @@
     <row r="204" spans="1:7" ht="12.75">
       <c r="A204" s="9"/>
       <c r="B204" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C204" s="11"/>
       <c r="D204" s="11"/>
@@ -4451,7 +4490,7 @@
     <row r="205" spans="1:7" ht="12.75">
       <c r="A205" s="9"/>
       <c r="B205" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C205" s="11"/>
       <c r="D205" s="11"/>
@@ -4465,7 +4504,7 @@
     <row r="206" spans="1:7" ht="12.75">
       <c r="A206" s="9"/>
       <c r="B206" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C206" s="11"/>
       <c r="D206" s="11"/>
@@ -4479,7 +4518,7 @@
     <row r="207" spans="1:7" ht="12.75">
       <c r="A207" s="9"/>
       <c r="B207" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C207" s="11"/>
       <c r="D207" s="11"/>
@@ -4493,7 +4532,7 @@
     <row r="208" spans="1:7" ht="12.75">
       <c r="A208" s="9"/>
       <c r="B208" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C208" s="16"/>
       <c r="D208" s="11"/>
@@ -4518,7 +4557,7 @@
     </row>
     <row r="210" spans="1:7" ht="12.75">
       <c r="A210" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -4532,7 +4571,7 @@
         <v>2</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C211" s="5"/>
       <c r="D211" s="5"/>
@@ -4541,21 +4580,23 @@
       <c r="G211" s="6"/>
     </row>
     <row r="212" spans="1:7" ht="12.75">
-      <c r="A212" s="7"/>
+      <c r="A212" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B212" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C212" s="11">
         <v>1</v>
       </c>
       <c r="D212" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E212" s="11">
         <v>12699</v>
       </c>
       <c r="F212" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G212" s="13">
         <f>C212*E212</f>
@@ -4565,7 +4606,7 @@
     <row r="213" spans="1:7" ht="12.75">
       <c r="A213" s="9"/>
       <c r="B213" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C213" s="11"/>
       <c r="D213" s="11"/>
@@ -4579,7 +4620,7 @@
     <row r="214" spans="1:7" ht="12.75">
       <c r="A214" s="9"/>
       <c r="B214" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C214" s="11"/>
       <c r="D214" s="11"/>
@@ -4593,7 +4634,7 @@
     <row r="215" spans="1:7" ht="12.75">
       <c r="A215" s="9"/>
       <c r="B215" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C215" s="11"/>
       <c r="D215" s="11"/>
@@ -4607,7 +4648,7 @@
     <row r="216" spans="1:7" ht="12.75">
       <c r="A216" s="9"/>
       <c r="B216" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C216" s="11"/>
       <c r="D216" s="11"/>
@@ -4620,22 +4661,22 @@
     </row>
     <row r="217" spans="1:7" ht="12.75">
       <c r="A217" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B217" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C217" s="11">
         <v>0.20</v>
       </c>
       <c r="D217" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E217" s="11">
         <v>784</v>
       </c>
       <c r="F217" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G217" s="13">
         <f>C217*E217</f>
@@ -4644,22 +4685,22 @@
     </row>
     <row r="218" spans="1:7" ht="12.75">
       <c r="A218" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B218" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C218" s="11">
         <v>0.20</v>
       </c>
       <c r="D218" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E218" s="11">
         <v>645</v>
       </c>
       <c r="F218" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G218" s="13">
         <f>C218*E218</f>
@@ -4669,7 +4710,7 @@
     <row r="219" spans="1:7" ht="12.75">
       <c r="A219" s="9"/>
       <c r="B219" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C219" s="11"/>
       <c r="D219" s="11"/>
@@ -4683,7 +4724,7 @@
     <row r="220" spans="1:7" ht="12.75">
       <c r="A220" s="9"/>
       <c r="B220" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C220" s="11"/>
       <c r="D220" s="11"/>
@@ -4697,7 +4738,7 @@
     <row r="221" spans="1:7" ht="12.75">
       <c r="A221" s="9"/>
       <c r="B221" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C221" s="11"/>
       <c r="D221" s="11"/>
@@ -4711,7 +4752,7 @@
     <row r="222" spans="1:7" ht="12.75">
       <c r="A222" s="9"/>
       <c r="B222" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C222" s="11"/>
       <c r="D222" s="11"/>
@@ -4725,7 +4766,7 @@
     <row r="223" spans="1:7" ht="12.75">
       <c r="A223" s="9"/>
       <c r="B223" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C223" s="16"/>
       <c r="D223" s="11"/>
@@ -4750,10 +4791,10 @@
     </row>
     <row r="225" spans="1:7" ht="12.75">
       <c r="A225" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B225" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C225" s="5"/>
       <c r="D225" s="5"/>
@@ -4762,21 +4803,23 @@
       <c r="G225" s="6"/>
     </row>
     <row r="226" spans="1:7" ht="12.75">
-      <c r="A226" s="7"/>
+      <c r="A226" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B226" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C226" s="11">
         <v>1</v>
       </c>
       <c r="D226" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E226" s="11">
         <v>15180</v>
       </c>
       <c r="F226" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G226" s="13">
         <f>C226*E226</f>
@@ -4786,7 +4829,7 @@
     <row r="227" spans="1:7" ht="12.75">
       <c r="A227" s="9"/>
       <c r="B227" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C227" s="11"/>
       <c r="D227" s="11"/>
@@ -4800,7 +4843,7 @@
     <row r="228" spans="1:7" ht="12.75">
       <c r="A228" s="9"/>
       <c r="B228" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C228" s="11"/>
       <c r="D228" s="11"/>
@@ -4814,7 +4857,7 @@
     <row r="229" spans="1:7" ht="12.75">
       <c r="A229" s="9"/>
       <c r="B229" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C229" s="11"/>
       <c r="D229" s="11"/>
@@ -4828,7 +4871,7 @@
     <row r="230" spans="1:7" ht="12.75">
       <c r="A230" s="9"/>
       <c r="B230" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C230" s="11"/>
       <c r="D230" s="11"/>
@@ -4841,22 +4884,22 @@
     </row>
     <row r="231" spans="1:7" ht="12.75">
       <c r="A231" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B231" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C231" s="11">
         <v>0.20</v>
       </c>
       <c r="D231" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E231" s="11">
         <v>784</v>
       </c>
       <c r="F231" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G231" s="13">
         <f>C231*E231</f>
@@ -4865,22 +4908,22 @@
     </row>
     <row r="232" spans="1:7" ht="12.75">
       <c r="A232" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B232" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C232" s="11">
         <v>0.20</v>
       </c>
       <c r="D232" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E232" s="11">
         <v>645</v>
       </c>
       <c r="F232" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G232" s="13">
         <f>C232*E232</f>
@@ -4890,7 +4933,7 @@
     <row r="233" spans="1:7" ht="12.75">
       <c r="A233" s="9"/>
       <c r="B233" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C233" s="11"/>
       <c r="D233" s="11"/>
@@ -4904,7 +4947,7 @@
     <row r="234" spans="1:7" ht="12.75">
       <c r="A234" s="9"/>
       <c r="B234" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C234" s="11"/>
       <c r="D234" s="11"/>
@@ -4918,7 +4961,7 @@
     <row r="235" spans="1:7" ht="12.75">
       <c r="A235" s="9"/>
       <c r="B235" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C235" s="11"/>
       <c r="D235" s="11"/>
@@ -4932,7 +4975,7 @@
     <row r="236" spans="1:7" ht="12.75">
       <c r="A236" s="9"/>
       <c r="B236" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C236" s="11"/>
       <c r="D236" s="11"/>
@@ -4946,7 +4989,7 @@
     <row r="237" spans="1:7" ht="12.75">
       <c r="A237" s="9"/>
       <c r="B237" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C237" s="16"/>
       <c r="D237" s="11"/>
@@ -4971,10 +5014,10 @@
     </row>
     <row r="239" spans="1:7" ht="12.75">
       <c r="A239" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B239" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C239" s="5"/>
       <c r="D239" s="5"/>
@@ -4983,21 +5026,23 @@
       <c r="G239" s="6"/>
     </row>
     <row r="240" spans="1:7" ht="12.75">
-      <c r="A240" s="7"/>
+      <c r="A240" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B240" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C240" s="11">
         <v>1</v>
       </c>
       <c r="D240" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E240" s="11">
         <v>22270</v>
       </c>
       <c r="F240" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G240" s="13">
         <f>C240*E240</f>
@@ -5007,7 +5052,7 @@
     <row r="241" spans="1:7" ht="12.75">
       <c r="A241" s="9"/>
       <c r="B241" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C241" s="11"/>
       <c r="D241" s="11"/>
@@ -5021,7 +5066,7 @@
     <row r="242" spans="1:7" ht="12.75">
       <c r="A242" s="9"/>
       <c r="B242" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C242" s="11"/>
       <c r="D242" s="11"/>
@@ -5035,7 +5080,7 @@
     <row r="243" spans="1:7" ht="12.75">
       <c r="A243" s="9"/>
       <c r="B243" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C243" s="11"/>
       <c r="D243" s="11"/>
@@ -5049,7 +5094,7 @@
     <row r="244" spans="1:7" ht="12.75">
       <c r="A244" s="9"/>
       <c r="B244" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C244" s="11"/>
       <c r="D244" s="11"/>
@@ -5062,22 +5107,22 @@
     </row>
     <row r="245" spans="1:7" ht="12.75">
       <c r="A245" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B245" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C245" s="11">
         <v>0.20</v>
       </c>
       <c r="D245" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E245" s="11">
         <v>784</v>
       </c>
       <c r="F245" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G245" s="13">
         <f>C245*E245</f>
@@ -5086,22 +5131,22 @@
     </row>
     <row r="246" spans="1:7" ht="12.75">
       <c r="A246" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B246" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C246" s="11">
         <v>0.20</v>
       </c>
       <c r="D246" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E246" s="11">
         <v>645</v>
       </c>
       <c r="F246" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G246" s="13">
         <f>C246*E246</f>
@@ -5111,7 +5156,7 @@
     <row r="247" spans="1:7" ht="12.75">
       <c r="A247" s="9"/>
       <c r="B247" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C247" s="11"/>
       <c r="D247" s="11"/>
@@ -5125,7 +5170,7 @@
     <row r="248" spans="1:7" ht="12.75">
       <c r="A248" s="9"/>
       <c r="B248" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C248" s="11"/>
       <c r="D248" s="11"/>
@@ -5139,7 +5184,7 @@
     <row r="249" spans="1:7" ht="12.75">
       <c r="A249" s="9"/>
       <c r="B249" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C249" s="11"/>
       <c r="D249" s="11"/>
@@ -5153,7 +5198,7 @@
     <row r="250" spans="1:7" ht="12.75">
       <c r="A250" s="9"/>
       <c r="B250" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C250" s="11"/>
       <c r="D250" s="11"/>
@@ -5167,7 +5212,7 @@
     <row r="251" spans="1:7" ht="12.75">
       <c r="A251" s="9"/>
       <c r="B251" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C251" s="16"/>
       <c r="D251" s="11"/>
@@ -5192,7 +5237,7 @@
     </row>
     <row r="253" spans="1:7" ht="12.75">
       <c r="A253" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -5206,7 +5251,7 @@
         <v>2</v>
       </c>
       <c r="B254" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C254" s="5"/>
       <c r="D254" s="5"/>
@@ -5215,21 +5260,23 @@
       <c r="G254" s="6"/>
     </row>
     <row r="255" spans="1:7" ht="12.75">
-      <c r="A255" s="7"/>
+      <c r="A255" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B255" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C255" s="11">
         <v>1</v>
       </c>
       <c r="D255" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E255" s="11">
         <v>16282</v>
       </c>
       <c r="F255" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G255" s="13">
         <f>C255*E255</f>
@@ -5239,7 +5286,7 @@
     <row r="256" spans="1:7" ht="12.75">
       <c r="A256" s="9"/>
       <c r="B256" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C256" s="11"/>
       <c r="D256" s="11"/>
@@ -5253,7 +5300,7 @@
     <row r="257" spans="1:7" ht="12.75">
       <c r="A257" s="9"/>
       <c r="B257" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C257" s="11"/>
       <c r="D257" s="11"/>
@@ -5267,7 +5314,7 @@
     <row r="258" spans="1:7" ht="12.75">
       <c r="A258" s="9"/>
       <c r="B258" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C258" s="11"/>
       <c r="D258" s="11"/>
@@ -5281,7 +5328,7 @@
     <row r="259" spans="1:7" ht="12.75">
       <c r="A259" s="9"/>
       <c r="B259" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C259" s="11"/>
       <c r="D259" s="11"/>
@@ -5294,22 +5341,22 @@
     </row>
     <row r="260" spans="1:7" ht="12.75">
       <c r="A260" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B260" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C260" s="11">
         <v>0.20</v>
       </c>
       <c r="D260" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E260" s="11">
         <v>784</v>
       </c>
       <c r="F260" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G260" s="13">
         <f>C260*E260</f>
@@ -5318,22 +5365,22 @@
     </row>
     <row r="261" spans="1:7" ht="12.75">
       <c r="A261" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B261" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C261" s="11">
         <v>0.20</v>
       </c>
       <c r="D261" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E261" s="11">
         <v>645</v>
       </c>
       <c r="F261" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G261" s="13">
         <f>C261*E261</f>
@@ -5343,7 +5390,7 @@
     <row r="262" spans="1:7" ht="12.75">
       <c r="A262" s="9"/>
       <c r="B262" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C262" s="11"/>
       <c r="D262" s="11"/>
@@ -5357,7 +5404,7 @@
     <row r="263" spans="1:7" ht="12.75">
       <c r="A263" s="9"/>
       <c r="B263" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C263" s="11"/>
       <c r="D263" s="11"/>
@@ -5371,7 +5418,7 @@
     <row r="264" spans="1:7" ht="12.75">
       <c r="A264" s="9"/>
       <c r="B264" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C264" s="11"/>
       <c r="D264" s="11"/>
@@ -5385,7 +5432,7 @@
     <row r="265" spans="1:7" ht="12.75">
       <c r="A265" s="9"/>
       <c r="B265" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C265" s="11"/>
       <c r="D265" s="11"/>
@@ -5399,7 +5446,7 @@
     <row r="266" spans="1:7" ht="12.75">
       <c r="A266" s="9"/>
       <c r="B266" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C266" s="16"/>
       <c r="D266" s="11"/>
@@ -5424,7 +5471,7 @@
     </row>
     <row r="268" spans="1:7" ht="12.75">
       <c r="A268" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -5438,7 +5485,7 @@
         <v>2</v>
       </c>
       <c r="B269" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C269" s="5"/>
       <c r="D269" s="5"/>
@@ -5447,21 +5494,23 @@
       <c r="G269" s="6"/>
     </row>
     <row r="270" spans="1:7" ht="12.75">
-      <c r="A270" s="7"/>
+      <c r="A270" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B270" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C270" s="11">
         <v>1</v>
       </c>
       <c r="D270" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E270" s="11">
         <v>40522</v>
       </c>
       <c r="F270" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G270" s="13">
         <f>C270*E270</f>
@@ -5471,7 +5520,7 @@
     <row r="271" spans="1:7" ht="12.75">
       <c r="A271" s="9"/>
       <c r="B271" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C271" s="11"/>
       <c r="D271" s="11"/>
@@ -5485,7 +5534,7 @@
     <row r="272" spans="1:7" ht="12.75">
       <c r="A272" s="9"/>
       <c r="B272" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C272" s="11"/>
       <c r="D272" s="11"/>
@@ -5499,7 +5548,7 @@
     <row r="273" spans="1:7" ht="12.75">
       <c r="A273" s="9"/>
       <c r="B273" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C273" s="11"/>
       <c r="D273" s="11"/>
@@ -5513,7 +5562,7 @@
     <row r="274" spans="1:7" ht="12.75">
       <c r="A274" s="9"/>
       <c r="B274" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C274" s="11"/>
       <c r="D274" s="11"/>
@@ -5526,22 +5575,22 @@
     </row>
     <row r="275" spans="1:7" ht="12.75">
       <c r="A275" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B275" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C275" s="11">
         <v>0.20</v>
       </c>
       <c r="D275" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E275" s="11">
         <v>784</v>
       </c>
       <c r="F275" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G275" s="13">
         <f>C275*E275</f>
@@ -5550,22 +5599,22 @@
     </row>
     <row r="276" spans="1:7" ht="12.75">
       <c r="A276" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B276" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C276" s="11">
         <v>0.20</v>
       </c>
       <c r="D276" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E276" s="11">
         <v>645</v>
       </c>
       <c r="F276" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G276" s="13">
         <f>C276*E276</f>
@@ -5575,7 +5624,7 @@
     <row r="277" spans="1:7" ht="12.75">
       <c r="A277" s="9"/>
       <c r="B277" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C277" s="11"/>
       <c r="D277" s="11"/>
@@ -5589,7 +5638,7 @@
     <row r="278" spans="1:7" ht="12.75">
       <c r="A278" s="9"/>
       <c r="B278" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C278" s="11"/>
       <c r="D278" s="11"/>
@@ -5603,7 +5652,7 @@
     <row r="279" spans="1:7" ht="12.75">
       <c r="A279" s="9"/>
       <c r="B279" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C279" s="11"/>
       <c r="D279" s="11"/>
@@ -5617,7 +5666,7 @@
     <row r="280" spans="1:7" ht="12.75">
       <c r="A280" s="9"/>
       <c r="B280" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C280" s="11"/>
       <c r="D280" s="11"/>
@@ -5631,7 +5680,7 @@
     <row r="281" spans="1:7" ht="12.75">
       <c r="A281" s="9"/>
       <c r="B281" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C281" s="16"/>
       <c r="D281" s="11"/>
@@ -5656,10 +5705,10 @@
     </row>
     <row r="283" spans="1:7" ht="12.75">
       <c r="A283" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B283" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C283" s="5"/>
       <c r="D283" s="5"/>
@@ -5668,21 +5717,23 @@
       <c r="G283" s="6"/>
     </row>
     <row r="284" spans="1:7" ht="12.75">
-      <c r="A284" s="7"/>
+      <c r="A284" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B284" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C284" s="11">
         <v>1</v>
       </c>
       <c r="D284" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E284" s="11">
         <v>62500</v>
       </c>
       <c r="F284" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G284" s="13">
         <f>C284*E284</f>
@@ -5692,7 +5743,7 @@
     <row r="285" spans="1:7" ht="12.75">
       <c r="A285" s="9"/>
       <c r="B285" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C285" s="11"/>
       <c r="D285" s="11"/>
@@ -5706,7 +5757,7 @@
     <row r="286" spans="1:7" ht="12.75">
       <c r="A286" s="9"/>
       <c r="B286" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C286" s="11"/>
       <c r="D286" s="11"/>
@@ -5720,7 +5771,7 @@
     <row r="287" spans="1:7" ht="12.75">
       <c r="A287" s="9"/>
       <c r="B287" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C287" s="11"/>
       <c r="D287" s="11"/>
@@ -5734,7 +5785,7 @@
     <row r="288" spans="1:7" ht="12.75">
       <c r="A288" s="9"/>
       <c r="B288" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C288" s="11"/>
       <c r="D288" s="11"/>
@@ -5747,22 +5798,22 @@
     </row>
     <row r="289" spans="1:7" ht="12.75">
       <c r="A289" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B289" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C289" s="11">
         <v>0.20</v>
       </c>
       <c r="D289" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E289" s="11">
         <v>784</v>
       </c>
       <c r="F289" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G289" s="13">
         <f>C289*E289</f>
@@ -5771,22 +5822,22 @@
     </row>
     <row r="290" spans="1:7" ht="12.75">
       <c r="A290" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B290" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C290" s="11">
         <v>0.20</v>
       </c>
       <c r="D290" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E290" s="11">
         <v>645</v>
       </c>
       <c r="F290" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G290" s="13">
         <f>C290*E290</f>
@@ -5796,7 +5847,7 @@
     <row r="291" spans="1:7" ht="12.75">
       <c r="A291" s="9"/>
       <c r="B291" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C291" s="11"/>
       <c r="D291" s="11"/>
@@ -5810,7 +5861,7 @@
     <row r="292" spans="1:7" ht="12.75">
       <c r="A292" s="9"/>
       <c r="B292" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C292" s="11"/>
       <c r="D292" s="11"/>
@@ -5824,7 +5875,7 @@
     <row r="293" spans="1:7" ht="12.75">
       <c r="A293" s="9"/>
       <c r="B293" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C293" s="11"/>
       <c r="D293" s="11"/>
@@ -5838,7 +5889,7 @@
     <row r="294" spans="1:7" ht="12.75">
       <c r="A294" s="9"/>
       <c r="B294" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C294" s="11"/>
       <c r="D294" s="11"/>
@@ -5852,7 +5903,7 @@
     <row r="295" spans="1:7" ht="12.75">
       <c r="A295" s="9"/>
       <c r="B295" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C295" s="16"/>
       <c r="D295" s="11"/>
@@ -5877,10 +5928,10 @@
     </row>
     <row r="297" spans="1:7" ht="12.75">
       <c r="A297" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B297" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C297" s="5"/>
       <c r="D297" s="5"/>
@@ -5889,21 +5940,23 @@
       <c r="G297" s="6"/>
     </row>
     <row r="298" spans="1:7" ht="12.75">
-      <c r="A298" s="7"/>
+      <c r="A298" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B298" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C298" s="11">
         <v>1</v>
       </c>
       <c r="D298" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E298" s="11">
         <v>71266</v>
       </c>
       <c r="F298" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G298" s="13">
         <f>C298*E298</f>
@@ -5913,7 +5966,7 @@
     <row r="299" spans="1:7" ht="12.75">
       <c r="A299" s="9"/>
       <c r="B299" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C299" s="11"/>
       <c r="D299" s="11"/>
@@ -5927,7 +5980,7 @@
     <row r="300" spans="1:7" ht="12.75">
       <c r="A300" s="9"/>
       <c r="B300" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C300" s="11"/>
       <c r="D300" s="11"/>
@@ -5941,7 +5994,7 @@
     <row r="301" spans="1:7" ht="12.75">
       <c r="A301" s="9"/>
       <c r="B301" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C301" s="11"/>
       <c r="D301" s="11"/>
@@ -5955,7 +6008,7 @@
     <row r="302" spans="1:7" ht="12.75">
       <c r="A302" s="9"/>
       <c r="B302" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C302" s="11"/>
       <c r="D302" s="11"/>
@@ -5968,22 +6021,22 @@
     </row>
     <row r="303" spans="1:7" ht="12.75">
       <c r="A303" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B303" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C303" s="11">
         <v>0.20</v>
       </c>
       <c r="D303" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E303" s="11">
         <v>784</v>
       </c>
       <c r="F303" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G303" s="13">
         <f>C303*E303</f>
@@ -5992,22 +6045,22 @@
     </row>
     <row r="304" spans="1:7" ht="12.75">
       <c r="A304" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B304" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C304" s="11">
         <v>0.20</v>
       </c>
       <c r="D304" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E304" s="11">
         <v>645</v>
       </c>
       <c r="F304" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G304" s="13">
         <f>C304*E304</f>
@@ -6017,7 +6070,7 @@
     <row r="305" spans="1:7" ht="12.75">
       <c r="A305" s="9"/>
       <c r="B305" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C305" s="11"/>
       <c r="D305" s="11"/>
@@ -6031,7 +6084,7 @@
     <row r="306" spans="1:7" ht="12.75">
       <c r="A306" s="9"/>
       <c r="B306" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C306" s="11"/>
       <c r="D306" s="11"/>
@@ -6045,7 +6098,7 @@
     <row r="307" spans="1:7" ht="12.75">
       <c r="A307" s="9"/>
       <c r="B307" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C307" s="11"/>
       <c r="D307" s="11"/>
@@ -6059,7 +6112,7 @@
     <row r="308" spans="1:7" ht="12.75">
       <c r="A308" s="9"/>
       <c r="B308" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C308" s="11"/>
       <c r="D308" s="11"/>
@@ -6073,7 +6126,7 @@
     <row r="309" spans="1:7" ht="12.75">
       <c r="A309" s="9"/>
       <c r="B309" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C309" s="16"/>
       <c r="D309" s="11"/>
@@ -6098,7 +6151,7 @@
     </row>
     <row r="311" spans="1:7" ht="12.75">
       <c r="A311" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
@@ -6112,7 +6165,7 @@
         <v>2</v>
       </c>
       <c r="B312" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C312" s="5"/>
       <c r="D312" s="5"/>
@@ -6121,21 +6174,23 @@
       <c r="G312" s="6"/>
     </row>
     <row r="313" spans="1:7" ht="12.75">
-      <c r="A313" s="7"/>
+      <c r="A313" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B313" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C313" s="11">
         <v>1</v>
       </c>
       <c r="D313" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E313" s="11">
         <v>32500</v>
       </c>
       <c r="F313" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G313" s="13">
         <f>C313*E313</f>
@@ -6145,7 +6200,7 @@
     <row r="314" spans="1:7" ht="12.75">
       <c r="A314" s="9"/>
       <c r="B314" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C314" s="11"/>
       <c r="D314" s="11"/>
@@ -6159,7 +6214,7 @@
     <row r="315" spans="1:7" ht="12.75">
       <c r="A315" s="9"/>
       <c r="B315" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C315" s="11"/>
       <c r="D315" s="11"/>
@@ -6173,7 +6228,7 @@
     <row r="316" spans="1:7" ht="12.75">
       <c r="A316" s="9"/>
       <c r="B316" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C316" s="11"/>
       <c r="D316" s="11"/>
@@ -6187,7 +6242,7 @@
     <row r="317" spans="1:7" ht="12.75">
       <c r="A317" s="9"/>
       <c r="B317" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C317" s="11"/>
       <c r="D317" s="11"/>
@@ -6200,22 +6255,22 @@
     </row>
     <row r="318" spans="1:7" ht="12.75">
       <c r="A318" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B318" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C318" s="11">
         <v>0.20</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E318" s="11">
         <v>784</v>
       </c>
       <c r="F318" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G318" s="13">
         <f>C318*E318</f>
@@ -6224,22 +6279,22 @@
     </row>
     <row r="319" spans="1:7" ht="12.75">
       <c r="A319" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B319" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C319" s="11">
         <v>0.20</v>
       </c>
       <c r="D319" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E319" s="11">
         <v>645</v>
       </c>
       <c r="F319" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G319" s="13">
         <f>C319*E319</f>
@@ -6249,7 +6304,7 @@
     <row r="320" spans="1:7" ht="12.75">
       <c r="A320" s="9"/>
       <c r="B320" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C320" s="11"/>
       <c r="D320" s="11"/>
@@ -6263,7 +6318,7 @@
     <row r="321" spans="1:7" ht="12.75">
       <c r="A321" s="9"/>
       <c r="B321" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C321" s="11"/>
       <c r="D321" s="11"/>
@@ -6277,7 +6332,7 @@
     <row r="322" spans="1:7" ht="12.75">
       <c r="A322" s="9"/>
       <c r="B322" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C322" s="11"/>
       <c r="D322" s="11"/>
@@ -6291,7 +6346,7 @@
     <row r="323" spans="1:7" ht="12.75">
       <c r="A323" s="9"/>
       <c r="B323" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C323" s="11"/>
       <c r="D323" s="11"/>
@@ -6305,7 +6360,7 @@
     <row r="324" spans="1:7" ht="12.75">
       <c r="A324" s="9"/>
       <c r="B324" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C324" s="16"/>
       <c r="D324" s="11"/>
@@ -6330,7 +6385,7 @@
     </row>
     <row r="326" spans="1:7" ht="12.75">
       <c r="A326" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
@@ -6344,7 +6399,7 @@
         <v>2</v>
       </c>
       <c r="B327" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C327" s="5"/>
       <c r="D327" s="5"/>
@@ -6353,21 +6408,23 @@
       <c r="G327" s="6"/>
     </row>
     <row r="328" spans="1:7" ht="12.75">
-      <c r="A328" s="7"/>
+      <c r="A328" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B328" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C328" s="11">
         <v>1</v>
       </c>
       <c r="D328" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E328" s="11">
         <v>2800</v>
       </c>
       <c r="F328" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G328" s="13">
         <f>C328*E328</f>
@@ -6377,7 +6434,7 @@
     <row r="329" spans="1:7" ht="12.75">
       <c r="A329" s="7"/>
       <c r="B329" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C329" s="11"/>
       <c r="D329" s="11"/>
@@ -6391,7 +6448,7 @@
     <row r="330" spans="1:7" ht="12.75">
       <c r="A330" s="7"/>
       <c r="B330" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C330" s="11"/>
       <c r="D330" s="11"/>
@@ -6405,7 +6462,7 @@
     <row r="331" spans="1:7" ht="12.75">
       <c r="A331" s="7"/>
       <c r="B331" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C331" s="11"/>
       <c r="D331" s="11"/>
@@ -6419,7 +6476,7 @@
     <row r="332" spans="1:7" ht="12.75">
       <c r="A332" s="7"/>
       <c r="B332" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C332" s="16"/>
       <c r="D332" s="17"/>
@@ -6432,22 +6489,22 @@
     </row>
     <row r="333" spans="1:7" ht="12.75">
       <c r="A333" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B333" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C333" s="11">
         <v>15.50</v>
       </c>
       <c r="D333" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E333" s="11">
         <v>2.12</v>
       </c>
       <c r="F333" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G333" s="13">
         <f>C333*E333</f>
@@ -6457,7 +6514,7 @@
     <row r="334" spans="1:7" ht="12.75">
       <c r="A334" s="7"/>
       <c r="B334" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C334" s="11"/>
       <c r="D334" s="11"/>
@@ -6471,7 +6528,7 @@
     <row r="335" spans="1:7" ht="12.75">
       <c r="A335" s="7"/>
       <c r="B335" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C335" s="11"/>
       <c r="D335" s="11"/>
@@ -6485,7 +6542,7 @@
     <row r="336" spans="1:7" ht="12.75">
       <c r="A336" s="7"/>
       <c r="B336" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C336" s="11"/>
       <c r="D336" s="11"/>
@@ -6499,7 +6556,7 @@
     <row r="337" spans="1:7" ht="12.75">
       <c r="A337" s="7"/>
       <c r="B337" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C337" s="11"/>
       <c r="D337" s="11"/>
@@ -6513,7 +6570,7 @@
     <row r="338" spans="1:7" ht="12.75">
       <c r="A338" s="7"/>
       <c r="B338" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C338" s="16"/>
       <c r="D338" s="17"/>
@@ -6538,7 +6595,7 @@
     </row>
     <row r="340" spans="1:7" ht="12.75">
       <c r="A340" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
@@ -6552,7 +6609,7 @@
         <v>2</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C341" s="5"/>
       <c r="D341" s="5"/>
@@ -6561,21 +6618,23 @@
       <c r="G341" s="6"/>
     </row>
     <row r="342" spans="1:7" ht="12.75">
-      <c r="A342" s="7"/>
+      <c r="A342" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B342" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C342" s="11">
         <v>100</v>
       </c>
       <c r="D342" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E342" s="11">
         <v>20</v>
       </c>
       <c r="F342" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G342" s="13">
         <f>E342*C342</f>
@@ -6585,7 +6644,7 @@
     <row r="343" spans="1:7" ht="12.75">
       <c r="A343" s="7"/>
       <c r="B343" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C343" s="11"/>
       <c r="D343" s="11"/>
@@ -6599,7 +6658,7 @@
     <row r="344" spans="1:7" ht="12.75">
       <c r="A344" s="7"/>
       <c r="B344" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C344" s="11"/>
       <c r="D344" s="11"/>
@@ -6613,7 +6672,7 @@
     <row r="345" spans="1:7" ht="12.75">
       <c r="A345" s="7"/>
       <c r="B345" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C345" s="11"/>
       <c r="D345" s="11"/>
@@ -6627,7 +6686,7 @@
     <row r="346" spans="1:7" ht="12.75">
       <c r="A346" s="7"/>
       <c r="B346" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C346" s="16"/>
       <c r="D346" s="17"/>
@@ -6640,22 +6699,22 @@
     </row>
     <row r="347" spans="1:7" ht="12.75">
       <c r="A347" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B347" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C347" s="11">
         <v>0.60</v>
       </c>
       <c r="D347" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E347" s="11">
         <v>645</v>
       </c>
       <c r="F347" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G347" s="13">
         <f>C347*E347</f>
@@ -6665,7 +6724,7 @@
     <row r="348" spans="1:7" ht="12.75">
       <c r="A348" s="7"/>
       <c r="B348" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C348" s="11"/>
       <c r="D348" s="11"/>
@@ -6679,7 +6738,7 @@
     <row r="349" spans="1:7" ht="12.75">
       <c r="A349" s="7"/>
       <c r="B349" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C349" s="11"/>
       <c r="D349" s="11"/>
@@ -6693,7 +6752,7 @@
     <row r="350" spans="1:7" ht="12.75">
       <c r="A350" s="7"/>
       <c r="B350" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C350" s="11"/>
       <c r="D350" s="11"/>
@@ -6707,7 +6766,7 @@
     <row r="351" spans="1:7" ht="12.75">
       <c r="A351" s="7"/>
       <c r="B351" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C351" s="11"/>
       <c r="D351" s="11"/>
@@ -6721,7 +6780,7 @@
     <row r="352" spans="1:7" ht="12.75">
       <c r="A352" s="7"/>
       <c r="B352" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C352" s="16"/>
       <c r="D352" s="17"/>
@@ -6746,10 +6805,10 @@
     </row>
     <row r="354" spans="1:7" ht="12.75">
       <c r="A354" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B354" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C354" s="5"/>
       <c r="D354" s="5"/>
@@ -6758,21 +6817,23 @@
       <c r="G354" s="6"/>
     </row>
     <row r="355" spans="1:7" ht="12.75">
-      <c r="A355" s="7"/>
+      <c r="A355" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B355" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C355" s="11">
         <v>100</v>
       </c>
       <c r="D355" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E355" s="11">
         <v>350</v>
       </c>
       <c r="F355" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G355" s="13">
         <f>E355*C355</f>
@@ -6782,7 +6843,7 @@
     <row r="356" spans="1:7" ht="12.75">
       <c r="A356" s="7"/>
       <c r="B356" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C356" s="11"/>
       <c r="D356" s="11"/>
@@ -6796,7 +6857,7 @@
     <row r="357" spans="1:7" ht="12.75">
       <c r="A357" s="7"/>
       <c r="B357" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C357" s="11"/>
       <c r="D357" s="11"/>
@@ -6810,7 +6871,7 @@
     <row r="358" spans="1:7" ht="12.75">
       <c r="A358" s="7"/>
       <c r="B358" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C358" s="11"/>
       <c r="D358" s="11"/>
@@ -6824,7 +6885,7 @@
     <row r="359" spans="1:7" ht="12.75">
       <c r="A359" s="7"/>
       <c r="B359" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C359" s="16"/>
       <c r="D359" s="17"/>
@@ -6837,22 +6898,22 @@
     </row>
     <row r="360" spans="1:7" ht="12.75">
       <c r="A360" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B360" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C360" s="11">
         <v>0.60</v>
       </c>
       <c r="D360" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E360" s="11">
         <v>645</v>
       </c>
       <c r="F360" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G360" s="13">
         <f>C360*E360</f>
@@ -6862,7 +6923,7 @@
     <row r="361" spans="1:7" ht="12.75">
       <c r="A361" s="7"/>
       <c r="B361" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C361" s="11"/>
       <c r="D361" s="11"/>
@@ -6876,7 +6937,7 @@
     <row r="362" spans="1:7" ht="12.75">
       <c r="A362" s="7"/>
       <c r="B362" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C362" s="11"/>
       <c r="D362" s="11"/>
@@ -6890,7 +6951,7 @@
     <row r="363" spans="1:7" ht="12.75">
       <c r="A363" s="7"/>
       <c r="B363" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C363" s="11"/>
       <c r="D363" s="11"/>
@@ -6904,7 +6965,7 @@
     <row r="364" spans="1:7" ht="12.75">
       <c r="A364" s="7"/>
       <c r="B364" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C364" s="11"/>
       <c r="D364" s="11"/>
@@ -6918,7 +6979,7 @@
     <row r="365" spans="1:7" ht="12.75">
       <c r="A365" s="7"/>
       <c r="B365" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C365" s="16"/>
       <c r="D365" s="17"/>
@@ -6943,10 +7004,10 @@
     </row>
     <row r="367" spans="1:7" ht="12.75">
       <c r="A367" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B367" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C367" s="5"/>
       <c r="D367" s="5"/>
@@ -6955,21 +7016,23 @@
       <c r="G367" s="6"/>
     </row>
     <row r="368" spans="1:7" ht="12.75">
-      <c r="A368" s="7"/>
+      <c r="A368" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B368" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C368" s="11">
         <v>100</v>
       </c>
       <c r="D368" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E368" s="11">
         <v>310</v>
       </c>
       <c r="F368" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G368" s="13">
         <f>E368*C368</f>
@@ -6979,7 +7042,7 @@
     <row r="369" spans="1:7" ht="12.75">
       <c r="A369" s="7"/>
       <c r="B369" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C369" s="11"/>
       <c r="D369" s="11"/>
@@ -6993,7 +7056,7 @@
     <row r="370" spans="1:7" ht="12.75">
       <c r="A370" s="7"/>
       <c r="B370" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C370" s="11"/>
       <c r="D370" s="11"/>
@@ -7007,7 +7070,7 @@
     <row r="371" spans="1:7" ht="12.75">
       <c r="A371" s="7"/>
       <c r="B371" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C371" s="11"/>
       <c r="D371" s="11"/>
@@ -7021,7 +7084,7 @@
     <row r="372" spans="1:7" ht="12.75">
       <c r="A372" s="7"/>
       <c r="B372" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C372" s="16"/>
       <c r="D372" s="17"/>
@@ -7034,22 +7097,22 @@
     </row>
     <row r="373" spans="1:7" ht="12.75">
       <c r="A373" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B373" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C373" s="11">
         <v>0.60</v>
       </c>
       <c r="D373" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E373" s="11">
         <v>645</v>
       </c>
       <c r="F373" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G373" s="13">
         <f>C373*E373</f>
@@ -7059,7 +7122,7 @@
     <row r="374" spans="1:7" ht="12.75">
       <c r="A374" s="7"/>
       <c r="B374" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C374" s="11"/>
       <c r="D374" s="11"/>
@@ -7073,7 +7136,7 @@
     <row r="375" spans="1:7" ht="12.75">
       <c r="A375" s="7"/>
       <c r="B375" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C375" s="11"/>
       <c r="D375" s="11"/>
@@ -7087,7 +7150,7 @@
     <row r="376" spans="1:7" ht="12.75">
       <c r="A376" s="7"/>
       <c r="B376" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C376" s="11"/>
       <c r="D376" s="11"/>
@@ -7101,7 +7164,7 @@
     <row r="377" spans="1:7" ht="12.75">
       <c r="A377" s="7"/>
       <c r="B377" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C377" s="11"/>
       <c r="D377" s="11"/>
@@ -7115,7 +7178,7 @@
     <row r="378" spans="1:7" ht="12.75">
       <c r="A378" s="7"/>
       <c r="B378" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C378" s="16"/>
       <c r="D378" s="17"/>
@@ -7140,7 +7203,7 @@
     </row>
     <row r="380" spans="1:7" ht="12.75">
       <c r="A380" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
@@ -7154,7 +7217,7 @@
         <v>2</v>
       </c>
       <c r="B381" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C381" s="5"/>
       <c r="D381" s="5"/>
@@ -7163,21 +7226,23 @@
       <c r="G381" s="6"/>
     </row>
     <row r="382" spans="1:7" ht="12.75">
-      <c r="A382" s="7"/>
+      <c r="A382" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B382" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C382" s="11">
         <v>25</v>
       </c>
       <c r="D382" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E382" s="11">
         <v>42.58</v>
       </c>
       <c r="F382" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G382" s="13">
         <f>C382*E382</f>
@@ -7187,7 +7252,7 @@
     <row r="383" spans="1:7" ht="12.75">
       <c r="A383" s="7"/>
       <c r="B383" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C383" s="11"/>
       <c r="D383" s="11"/>
@@ -7201,7 +7266,7 @@
     <row r="384" spans="1:7" ht="12.75">
       <c r="A384" s="7"/>
       <c r="B384" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C384" s="11"/>
       <c r="D384" s="11"/>
@@ -7215,7 +7280,7 @@
     <row r="385" spans="1:7" ht="12.75">
       <c r="A385" s="7"/>
       <c r="B385" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C385" s="11"/>
       <c r="D385" s="11"/>
@@ -7229,7 +7294,7 @@
     <row r="386" spans="1:7" ht="12.75">
       <c r="A386" s="7"/>
       <c r="B386" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C386" s="16"/>
       <c r="D386" s="17"/>
@@ -7242,22 +7307,22 @@
     </row>
     <row r="387" spans="1:7" ht="12.75">
       <c r="A387" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B387" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C387" s="11">
         <v>0.10</v>
       </c>
       <c r="D387" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E387" s="11">
         <v>645</v>
       </c>
       <c r="F387" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G387" s="13">
         <f>C387*E387</f>
@@ -7267,7 +7332,7 @@
     <row r="388" spans="1:7" ht="12.75">
       <c r="A388" s="7"/>
       <c r="B388" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C388" s="11"/>
       <c r="D388" s="11"/>
@@ -7281,7 +7346,7 @@
     <row r="389" spans="1:7" ht="12.75">
       <c r="A389" s="7"/>
       <c r="B389" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C389" s="11"/>
       <c r="D389" s="11"/>
@@ -7295,7 +7360,7 @@
     <row r="390" spans="1:7" ht="12.75">
       <c r="A390" s="7"/>
       <c r="B390" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C390" s="11"/>
       <c r="D390" s="11"/>
@@ -7309,7 +7374,7 @@
     <row r="391" spans="1:7" ht="12.75">
       <c r="A391" s="7"/>
       <c r="B391" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C391" s="11"/>
       <c r="D391" s="11"/>
@@ -7323,7 +7388,7 @@
     <row r="392" spans="1:7" ht="12.75">
       <c r="A392" s="7"/>
       <c r="B392" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C392" s="16"/>
       <c r="D392" s="17"/>
@@ -7348,10 +7413,10 @@
     </row>
     <row r="394" spans="1:7" ht="12.75">
       <c r="A394" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B394" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C394" s="5"/>
       <c r="D394" s="5"/>
@@ -7360,21 +7425,23 @@
       <c r="G394" s="6"/>
     </row>
     <row r="395" spans="1:7" ht="12.75">
-      <c r="A395" s="7"/>
+      <c r="A395" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B395" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C395" s="11">
         <v>25</v>
       </c>
       <c r="D395" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E395" s="11">
         <v>33.35</v>
       </c>
       <c r="F395" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G395" s="13">
         <f>C395*E395</f>
@@ -7384,7 +7451,7 @@
     <row r="396" spans="1:7" ht="12.75">
       <c r="A396" s="7"/>
       <c r="B396" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C396" s="11"/>
       <c r="D396" s="11"/>
@@ -7398,7 +7465,7 @@
     <row r="397" spans="1:7" ht="12.75">
       <c r="A397" s="7"/>
       <c r="B397" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C397" s="11"/>
       <c r="D397" s="11"/>
@@ -7412,7 +7479,7 @@
     <row r="398" spans="1:7" ht="12.75">
       <c r="A398" s="7"/>
       <c r="B398" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C398" s="11"/>
       <c r="D398" s="11"/>
@@ -7426,7 +7493,7 @@
     <row r="399" spans="1:7" ht="12.75">
       <c r="A399" s="7"/>
       <c r="B399" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C399" s="16"/>
       <c r="D399" s="17"/>
@@ -7439,22 +7506,22 @@
     </row>
     <row r="400" spans="1:7" ht="12.75">
       <c r="A400" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B400" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C400" s="11">
         <v>0.10</v>
       </c>
       <c r="D400" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E400" s="11">
         <v>645</v>
       </c>
       <c r="F400" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G400" s="13">
         <f>C400*E400</f>
@@ -7464,7 +7531,7 @@
     <row r="401" spans="1:7" ht="12.75">
       <c r="A401" s="7"/>
       <c r="B401" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C401" s="11"/>
       <c r="D401" s="11"/>
@@ -7478,7 +7545,7 @@
     <row r="402" spans="1:7" ht="12.75">
       <c r="A402" s="7"/>
       <c r="B402" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C402" s="11"/>
       <c r="D402" s="11"/>
@@ -7492,7 +7559,7 @@
     <row r="403" spans="1:7" ht="12.75">
       <c r="A403" s="7"/>
       <c r="B403" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C403" s="11"/>
       <c r="D403" s="11"/>
@@ -7506,7 +7573,7 @@
     <row r="404" spans="1:7" ht="12.75">
       <c r="A404" s="7"/>
       <c r="B404" s="14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C404" s="11"/>
       <c r="D404" s="11"/>
@@ -7520,7 +7587,7 @@
     <row r="405" spans="1:7" ht="12.75">
       <c r="A405" s="7"/>
       <c r="B405" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C405" s="16"/>
       <c r="D405" s="17"/>
@@ -7545,7 +7612,7 @@
     </row>
     <row r="407" spans="1:7" ht="12.75">
       <c r="A407" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
@@ -7559,7 +7626,7 @@
         <v>2</v>
       </c>
       <c r="B408" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C408" s="5"/>
       <c r="D408" s="5"/>
@@ -7569,10 +7636,10 @@
     </row>
     <row r="409" spans="1:7" ht="12.75">
       <c r="A409" s="22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B409" s="23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C409" s="5"/>
       <c r="D409" s="5"/>
@@ -7582,10 +7649,10 @@
     </row>
     <row r="410" spans="1:7" ht="12.75">
       <c r="A410" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B410" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C410" s="11"/>
       <c r="D410" s="11"/>
@@ -7596,20 +7663,20 @@
     <row r="411" spans="1:7" ht="12.75">
       <c r="A411" s="7"/>
       <c r="B411" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C411" s="11">
         <v>15</v>
       </c>
       <c r="D411" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E411" s="24">
-        <f>'[1]PVC wo Trench'!F167</f>
+        <f>'[1]PVC wo Trench PRICE'!F167</f>
         <v>120.22</v>
       </c>
       <c r="F411" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G411" s="13">
         <f>ROUND(C411*E411,2)</f>
@@ -7619,20 +7686,20 @@
     <row r="412" spans="1:7" ht="12.75">
       <c r="A412" s="7"/>
       <c r="B412" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C412" s="11">
         <v>15</v>
       </c>
       <c r="D412" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E412" s="24">
-        <f>'[1]PVC wo Trench'!F176</f>
+        <f>'[1]PVC wo Trench PRICE'!F176</f>
         <v>29.66</v>
       </c>
       <c r="F412" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G412" s="13">
         <f>ROUND(C412*E412,2)</f>
@@ -7641,10 +7708,10 @@
     </row>
     <row r="413" spans="1:7" ht="12.75">
       <c r="A413" s="7" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B413" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C413" s="11"/>
       <c r="D413" s="11"/>
@@ -7655,20 +7722,20 @@
     <row r="414" spans="1:7" ht="12.75">
       <c r="A414" s="7"/>
       <c r="B414" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C414" s="11">
         <v>20</v>
       </c>
       <c r="D414" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E414" s="24">
-        <f>'[1]PVC wo Trench'!F123</f>
+        <f>'[1]PVC wo Trench PRICE'!F123</f>
         <v>112.20</v>
       </c>
       <c r="F414" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G414" s="13">
         <f>ROUND(C414*E414,2)</f>
@@ -7678,20 +7745,20 @@
     <row r="415" spans="1:7" ht="12.75">
       <c r="A415" s="7"/>
       <c r="B415" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C415" s="11">
         <v>20</v>
       </c>
       <c r="D415" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E415" s="24">
-        <f>'[1]PVC wo Trench'!F132</f>
+        <f>'[1]PVC wo Trench PRICE'!F132</f>
         <v>29.66</v>
       </c>
       <c r="F415" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G415" s="13">
         <f>ROUND(C415*E415,2)</f>
@@ -7700,10 +7767,10 @@
     </row>
     <row r="416" spans="1:7" ht="12.75">
       <c r="A416" s="7" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B416" s="10" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C416" s="11"/>
       <c r="D416" s="11"/>
@@ -7714,20 +7781,20 @@
     <row r="417" spans="1:7" ht="12.75">
       <c r="A417" s="7"/>
       <c r="B417" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C417" s="11">
         <v>10</v>
       </c>
       <c r="D417" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E417" s="24">
-        <f>'[1]PVC wo Trench'!F57</f>
+        <f>'[1]PVC wo Trench PRICE'!F57</f>
         <v>86.82</v>
       </c>
       <c r="F417" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G417" s="13">
         <f>ROUND(C417*E417,2)</f>
@@ -7737,20 +7804,20 @@
     <row r="418" spans="1:7" ht="12.75">
       <c r="A418" s="7"/>
       <c r="B418" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C418" s="11">
         <v>10</v>
       </c>
       <c r="D418" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E418" s="24">
-        <f>'[1]PVC wo Trench'!F66</f>
+        <f>'[1]PVC wo Trench PRICE'!F66</f>
         <v>29.66</v>
       </c>
       <c r="F418" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G418" s="13">
         <f>ROUND(C418*E418,2)</f>
@@ -7759,10 +7826,10 @@
     </row>
     <row r="419" spans="1:7" ht="12.75">
       <c r="A419" s="7" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B419" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C419" s="11"/>
       <c r="D419" s="11"/>
@@ -7773,20 +7840,20 @@
     <row r="420" spans="1:7" ht="12.75">
       <c r="A420" s="7"/>
       <c r="B420" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C420" s="11">
         <v>15</v>
       </c>
       <c r="D420" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E420" s="24">
-        <f>'[1]PVC wo Trench'!F35</f>
+        <f>'[1]PVC wo Trench PRICE'!F35</f>
         <v>64.11</v>
       </c>
       <c r="F420" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G420" s="13">
         <f>ROUND(C420*E420,2)</f>
@@ -7796,20 +7863,20 @@
     <row r="421" spans="1:7" ht="12.75">
       <c r="A421" s="7"/>
       <c r="B421" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C421" s="11">
         <v>15</v>
       </c>
       <c r="D421" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E421" s="24">
-        <f>'[1]PVC wo Trench'!F44</f>
+        <f>'[1]PVC wo Trench PRICE'!F44</f>
         <v>29.66</v>
       </c>
       <c r="F421" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G421" s="13">
         <f>ROUND(C421*E421,2)</f>
@@ -7818,10 +7885,10 @@
     </row>
     <row r="422" spans="1:7" ht="12.75">
       <c r="A422" s="7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B422" s="10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C422" s="11"/>
       <c r="D422" s="11"/>
@@ -7832,20 +7899,20 @@
     <row r="423" spans="1:7" ht="12.75">
       <c r="A423" s="7"/>
       <c r="B423" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C423" s="11">
         <v>1</v>
       </c>
       <c r="D423" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E423" s="11">
         <f>'[1]Motor Starter Monoblock'!F20</f>
         <v>859.71</v>
       </c>
       <c r="F423" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G423" s="13">
         <f>ROUND(C423*E423,2)</f>
@@ -7855,20 +7922,20 @@
     <row r="424" spans="1:7" ht="12.75">
       <c r="A424" s="7"/>
       <c r="B424" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C424" s="11">
         <v>1</v>
       </c>
       <c r="D424" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E424" s="11">
         <f>'[1]Motor Starter Monoblock'!F34</f>
         <v>33.70</v>
       </c>
       <c r="F424" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G424" s="13">
         <f>ROUND(C424*E424,2)</f>
@@ -7878,7 +7945,7 @@
     <row r="425" spans="1:7" ht="12.75">
       <c r="A425" s="7"/>
       <c r="B425" s="14" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C425" s="11"/>
       <c r="D425" s="11"/>
@@ -7892,7 +7959,7 @@
     <row r="426" spans="1:7" ht="12.75">
       <c r="A426" s="7"/>
       <c r="B426" s="14" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C426" s="11"/>
       <c r="D426" s="11"/>
@@ -7905,10 +7972,10 @@
     </row>
     <row r="427" spans="1:7" ht="12.75">
       <c r="A427" s="22" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B427" s="23" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C427" s="5"/>
       <c r="D427" s="5"/>
@@ -7918,22 +7985,22 @@
     </row>
     <row r="428" spans="1:7" ht="12.75">
       <c r="A428" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B428" s="10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C428" s="11">
         <v>15</v>
       </c>
       <c r="D428" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E428" s="11">
         <v>40</v>
       </c>
       <c r="F428" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G428" s="13">
         <f>C428*E428</f>
@@ -7943,7 +8010,7 @@
     <row r="429" spans="1:7" ht="12.75">
       <c r="A429" s="7"/>
       <c r="B429" s="10" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C429" s="11"/>
       <c r="D429" s="11"/>
@@ -7956,22 +8023,22 @@
     </row>
     <row r="430" spans="1:7" ht="12.75">
       <c r="A430" s="7" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B430" s="10" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C430" s="11">
         <v>2</v>
       </c>
       <c r="D430" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E430" s="11">
         <v>380</v>
       </c>
       <c r="F430" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G430" s="13">
         <f>C430*E430</f>
@@ -7980,22 +8047,22 @@
     </row>
     <row r="431" spans="1:7" ht="12.75">
       <c r="A431" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B431" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C431" s="11">
         <v>6</v>
       </c>
       <c r="D431" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E431" s="11">
         <v>280</v>
       </c>
       <c r="F431" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G431" s="13">
         <f>C431*E431</f>
@@ -8004,22 +8071,23 @@
     </row>
     <row r="432" spans="1:7" ht="12.75">
       <c r="A432" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B432" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C432" s="11">
         <v>3</v>
       </c>
       <c r="D432" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E432" s="11">
+        <f t="array" ref="E432">IFERROR(INDEX(LMRRates,MATCH(A432,LMRCodes,0),),)</f>
         <v>720</v>
       </c>
       <c r="F432" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G432" s="13">
         <f>C432*E432</f>
@@ -8027,21 +8095,23 @@
       </c>
     </row>
     <row r="433" spans="1:7" ht="12.75">
-      <c r="A433" s="7"/>
+      <c r="A433" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B433" s="10" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C433" s="11">
         <v>4</v>
       </c>
       <c r="D433" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E433" s="11">
         <v>73</v>
       </c>
       <c r="F433" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G433" s="13">
         <f>C433*E433</f>
@@ -8049,21 +8119,23 @@
       </c>
     </row>
     <row r="434" spans="1:7" ht="12.75">
-      <c r="A434" s="7"/>
+      <c r="A434" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B434" s="10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C434" s="11">
         <v>50</v>
       </c>
       <c r="D434" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E434" s="11">
         <v>40</v>
       </c>
       <c r="F434" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G434" s="13">
         <f>C434*E434</f>
@@ -8071,21 +8143,23 @@
       </c>
     </row>
     <row r="435" spans="1:7" ht="12.75">
-      <c r="A435" s="7"/>
+      <c r="A435" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B435" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C435" s="11">
         <v>2</v>
       </c>
       <c r="D435" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E435" s="11">
         <v>280</v>
       </c>
       <c r="F435" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G435" s="13">
         <f>C435*E435</f>
@@ -8093,21 +8167,23 @@
       </c>
     </row>
     <row r="436" spans="1:7" ht="12.75">
-      <c r="A436" s="7"/>
+      <c r="A436" s="7" t="s">
+        <v>4</v>
+      </c>
       <c r="B436" s="10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C436" s="11">
         <v>36</v>
       </c>
       <c r="D436" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E436" s="11">
         <v>67.70</v>
       </c>
       <c r="F436" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G436" s="13">
         <f>C436*E436</f>
@@ -8117,7 +8193,7 @@
     <row r="437" spans="1:7" ht="12.75">
       <c r="A437" s="7"/>
       <c r="B437" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C437" s="11"/>
       <c r="D437" s="11"/>
@@ -8131,7 +8207,7 @@
     <row r="438" spans="1:7" ht="12.75">
       <c r="A438" s="7"/>
       <c r="B438" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C438" s="11"/>
       <c r="D438" s="11"/>
@@ -8145,7 +8221,7 @@
     <row r="439" spans="1:7" ht="12.75">
       <c r="A439" s="7"/>
       <c r="B439" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C439" s="11"/>
       <c r="D439" s="11"/>
@@ -8159,7 +8235,7 @@
     <row r="440" spans="1:7" ht="12.75">
       <c r="A440" s="7"/>
       <c r="B440" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C440" s="11"/>
       <c r="D440" s="11"/>
@@ -8173,7 +8249,7 @@
     <row r="441" spans="1:7" ht="12.75">
       <c r="A441" s="7"/>
       <c r="B441" s="26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C441" s="16"/>
       <c r="D441" s="11"/>
@@ -8186,10 +8262,10 @@
     </row>
     <row r="442" spans="1:7" ht="12.75">
       <c r="A442" s="22" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B442" s="23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C442" s="5"/>
       <c r="D442" s="5"/>
@@ -8199,22 +8275,22 @@
     </row>
     <row r="443" spans="1:7" ht="12.75">
       <c r="A443" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B443" s="10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C443" s="11">
         <v>2</v>
       </c>
       <c r="D443" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E443" s="27">
         <v>853</v>
       </c>
       <c r="F443" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G443" s="13">
         <f>C443*E443</f>
@@ -8223,22 +8299,22 @@
     </row>
     <row r="444" spans="1:7" ht="12.75">
       <c r="A444" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B444" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C444" s="11">
         <v>1</v>
       </c>
       <c r="D444" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E444" s="27">
         <v>784</v>
       </c>
       <c r="F444" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G444" s="13">
         <f>C444*E444</f>
@@ -8247,22 +8323,22 @@
     </row>
     <row r="445" spans="1:7" ht="12.75">
       <c r="A445" s="7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B445" s="10" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C445" s="11">
         <v>1</v>
       </c>
       <c r="D445" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E445" s="27">
         <v>714</v>
       </c>
       <c r="F445" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G445" s="13">
         <f>C445*E445</f>
@@ -8271,22 +8347,22 @@
     </row>
     <row r="446" spans="1:7" ht="12.75">
       <c r="A446" s="7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B446" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C446" s="11">
         <v>2</v>
       </c>
       <c r="D446" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E446" s="27">
         <v>645</v>
       </c>
       <c r="F446" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G446" s="13">
         <f>C446*E446</f>
@@ -8296,7 +8372,7 @@
     <row r="447" spans="1:7" ht="12.75">
       <c r="A447" s="7"/>
       <c r="B447" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C447" s="11"/>
       <c r="D447" s="11"/>
@@ -8310,7 +8386,7 @@
     <row r="448" spans="1:7" ht="12.75">
       <c r="A448" s="7"/>
       <c r="B448" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C448" s="11"/>
       <c r="D448" s="11"/>
@@ -8324,7 +8400,7 @@
     <row r="449" spans="1:7" ht="12.75">
       <c r="A449" s="7"/>
       <c r="B449" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C449" s="11"/>
       <c r="D449" s="11"/>
@@ -8338,7 +8414,7 @@
     <row r="450" spans="1:7" ht="12.75">
       <c r="A450" s="7"/>
       <c r="B450" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C450" s="11"/>
       <c r="D450" s="11"/>
@@ -8352,7 +8428,7 @@
     <row r="451" spans="1:7" ht="12.75">
       <c r="A451" s="7"/>
       <c r="B451" s="26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C451" s="16"/>
       <c r="D451" s="11"/>
@@ -8377,7 +8453,7 @@
     </row>
     <row r="453" spans="1:7" ht="12.75">
       <c r="A453" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B453" s="5"/>
       <c r="C453" s="5"/>
@@ -8391,7 +8467,7 @@
         <v>2</v>
       </c>
       <c r="B454" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C454" s="5"/>
       <c r="D454" s="5"/>
@@ -8402,19 +8478,19 @@
     <row r="455" spans="1:7" ht="12.75">
       <c r="A455" s="7"/>
       <c r="B455" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C455" s="11">
         <v>1</v>
       </c>
       <c r="D455" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E455" s="11">
         <v>3500</v>
       </c>
       <c r="F455" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G455" s="13">
         <f>C455*E455</f>
@@ -8424,19 +8500,19 @@
     <row r="456" spans="1:7" ht="12.75">
       <c r="A456" s="7"/>
       <c r="B456" s="10" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C456" s="11">
         <v>1</v>
       </c>
       <c r="D456" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E456" s="11">
         <v>2000</v>
       </c>
       <c r="F456" s="12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G456" s="13">
         <f>C456*E456</f>
@@ -8446,7 +8522,7 @@
     <row r="457" spans="1:7" ht="12.75">
       <c r="A457" s="7"/>
       <c r="B457" s="29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C457" s="11"/>
       <c r="D457" s="11"/>
@@ -8459,22 +8535,22 @@
     </row>
     <row r="458" spans="1:7" ht="12.75">
       <c r="A458" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B458" s="10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C458" s="11">
         <v>0.50</v>
       </c>
       <c r="D458" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E458" s="27">
         <v>853</v>
       </c>
       <c r="F458" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G458" s="13">
         <f>C458*E458</f>
@@ -8483,22 +8559,22 @@
     </row>
     <row r="459" spans="1:7" ht="12.75">
       <c r="A459" s="7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B459" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C459" s="11">
         <v>0.50</v>
       </c>
       <c r="D459" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E459" s="27">
         <v>645</v>
       </c>
       <c r="F459" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G459" s="13">
         <f>C459*E459</f>
@@ -8508,7 +8584,7 @@
     <row r="460" spans="1:7" ht="12.75">
       <c r="A460" s="7"/>
       <c r="B460" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C460" s="11"/>
       <c r="D460" s="11"/>
@@ -8522,7 +8598,7 @@
     <row r="461" spans="1:7" ht="12.75">
       <c r="A461" s="7"/>
       <c r="B461" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C461" s="11"/>
       <c r="D461" s="11"/>
@@ -8536,7 +8612,7 @@
     <row r="462" spans="1:7" ht="12.75">
       <c r="A462" s="7"/>
       <c r="B462" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C462" s="11"/>
       <c r="D462" s="11"/>
@@ -8550,7 +8626,7 @@
     <row r="463" spans="1:7" ht="12.75">
       <c r="A463" s="7"/>
       <c r="B463" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C463" s="11"/>
       <c r="D463" s="11"/>
@@ -8564,7 +8640,7 @@
     <row r="464" spans="1:7" ht="12.75">
       <c r="A464" s="7"/>
       <c r="B464" s="26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C464" s="16"/>
       <c r="D464" s="11"/>

--- a/Side Bar Files/GWD Data/WTP.xlsx
+++ b/Side Bar Files/GWD Data/WTP.xlsx
@@ -1295,7 +1295,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98489C21-0790-4944-9758-54ABDDCDBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A774DB6E-9EA8-4BA6-887A-46FC2581BAA6}">
   <dimension ref="A1:G465"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/WTP.xlsx
+++ b/Side Bar Files/GWD Data/WTP.xlsx
@@ -13,8 +13,8 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
-    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+    <definedName name="LMRRates">[1]zLMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]zLMR!$A:$A</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -940,10 +940,10 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
-      <sheetName val="Derived"/>
-      <sheetName val="LMR"/>
-      <sheetName val="PAMR39"/>
-      <sheetName val="ZCost Index"/>
+      <sheetName val="zCost Index"/>
+      <sheetName val="zDerived"/>
+      <sheetName val="zLMR"/>
+      <sheetName val="zPAMR39"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -1295,7 +1295,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A774DB6E-9EA8-4BA6-887A-46FC2581BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D5664B6-9D5C-413C-B209-0CE1DF3EBAA6}">
   <dimension ref="A1:G465"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
